--- a/documentos/estadisticas_plan_cargas/2026-10-12_estadisticas_cargas_OTROS_2021-2026.xlsx
+++ b/documentos/estadisticas_plan_cargas/2026-10-12_estadisticas_cargas_OTROS_2021-2026.xlsx
@@ -15,6 +15,9 @@
     <sheet name="cancelaciones" sheetId="8" r:id="rId9"/>
     <sheet name="merma" sheetId="9" r:id="rId10"/>
     <sheet name="datos" sheetId="10" r:id="rId11"/>
+    <sheet name="transportistas_detalle" sheetId="11" r:id="rId12"/>
+    <sheet name="transp_x_productor" sheetId="12" r:id="rId13"/>
+    <sheet name="transp_concentracion" sheetId="13" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'por_año'!$A$1:$N$81</definedName>
@@ -26,13 +29,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'cancelaciones'!$A$1:$H$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'merma'!$A$1:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'datos'!$A$1:$X$1062</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'transportistas_detalle'!$A$1:$AB$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'transp_x_productor'!$A$1:$R$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'transp_concentracion'!$A$1:$O$9</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3533" uniqueCount="3533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="3820">
   <si>
     <t>Dato</t>
   </si>
@@ -10631,6 +10637,867 @@
   </si>
   <si>
     <t>SE DESCARGO EN UAM 1049 CAJAS DE LAS CUALES 850 CORRESPONDEN A BOLIVIA Y 199 A PLATANO</t>
+  </si>
+  <si>
+    <t>transportista</t>
+  </si>
+  <si>
+    <t>origen</t>
+  </si>
+  <si>
+    <t>total_camiones</t>
+  </si>
+  <si>
+    <t>cam 2019</t>
+  </si>
+  <si>
+    <t>cam 2020</t>
+  </si>
+  <si>
+    <t>cam 2021</t>
+  </si>
+  <si>
+    <t>cam 2022</t>
+  </si>
+  <si>
+    <t>cam 2023</t>
+  </si>
+  <si>
+    <t>cam 2024</t>
+  </si>
+  <si>
+    <t>cam 2025</t>
+  </si>
+  <si>
+    <t>cam 2026</t>
+  </si>
+  <si>
+    <t>pct 2025</t>
+  </si>
+  <si>
+    <t>pct 2026</t>
+  </si>
+  <si>
+    <t>cancelados</t>
+  </si>
+  <si>
+    <t>pct cancelacion</t>
+  </si>
+  <si>
+    <t>carga-frontera mediana</t>
+  </si>
+  <si>
+    <t>frontera-descarga mediana</t>
+  </si>
+  <si>
+    <t>carga-descarga mediana</t>
+  </si>
+  <si>
+    <t>carga-descarga P90</t>
+  </si>
+  <si>
+    <t>pct en 3 dias o menos</t>
+  </si>
+  <si>
+    <t>cajas prom por camion</t>
+  </si>
+  <si>
+    <t>productores (n)</t>
+  </si>
+  <si>
+    <t>productores principales</t>
+  </si>
+  <si>
+    <t>fronteras</t>
+  </si>
+  <si>
+    <t>primera carga</t>
+  </si>
+  <si>
+    <t>ultima carga</t>
+  </si>
+  <si>
+    <t>activo 2026</t>
+  </si>
+  <si>
+    <t>nombres en planilla</t>
+  </si>
+  <si>
+    <t>Silvio</t>
+  </si>
+  <si>
+    <t>BR 1421 / PY 1</t>
+  </si>
+  <si>
+    <t>Nordeste 370 · Corupá 323 · Valdemar 135 · Gilson 118</t>
+  </si>
+  <si>
+    <t>Rio Branco 1206 · Rivera 171 · Chuy 45</t>
+  </si>
+  <si>
+    <t>2019-01-04</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>Silvio | Silvio Abierto</t>
+  </si>
+  <si>
+    <t>Zanini</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>Claudia 554 · Jhony Viera 327 · Corupá 90 · Valdemar 80</t>
+  </si>
+  <si>
+    <t>Rio Branco 1085 · Rivera 286 · Chuy 15</t>
+  </si>
+  <si>
+    <t>2019-01-03</t>
+  </si>
+  <si>
+    <t>Transzanini | Zanini</t>
+  </si>
+  <si>
+    <t>FG</t>
+  </si>
+  <si>
+    <t>Valdemar 196 · Jhony Viera 138 · Fischer 91 · Corupá 75</t>
+  </si>
+  <si>
+    <t>Rio Branco 782</t>
+  </si>
+  <si>
+    <t>BR 8 / PY 417</t>
+  </si>
+  <si>
+    <t>Paraguay EC 134 · Paraguay MS 120 · Paraguay HF 64 · Paraguay DF 49</t>
+  </si>
+  <si>
+    <t>Salto 412 · Rio Branco 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> | #N/A | 0 | xx</t>
+  </si>
+  <si>
+    <t>Amaro</t>
+  </si>
+  <si>
+    <t>Jaime 107 · Fischer 34 · Gilson 27 · Jhony Viera 21</t>
+  </si>
+  <si>
+    <t>Rio Branco 290 · Chuy 2</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>Alto Paraguay</t>
+  </si>
+  <si>
+    <t>PY</t>
+  </si>
+  <si>
+    <t>Paraguay 227 · Paraguay H 23</t>
+  </si>
+  <si>
+    <t>Salto 250</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>2023-11-02</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Gral</t>
+  </si>
+  <si>
+    <t>Valdemar 66 · Corupá 27 · BAHIA 23 · Jhony Viera 17</t>
+  </si>
+  <si>
+    <t>Rio Branco 196 · Chuy 13</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>Chabat</t>
+  </si>
+  <si>
+    <t>Fischer 33 · Cassio Hauck 23 · Jorge Marangoni 12 · Corupá 11</t>
+  </si>
+  <si>
+    <t>Rio Branco 131 · Chuy 20</t>
+  </si>
+  <si>
+    <t>2021-10-11</t>
+  </si>
+  <si>
+    <t>Marvel</t>
+  </si>
+  <si>
+    <t>BAHIA 75 · Banana SP 9 · Valdemar 3 · Nordeste 2</t>
+  </si>
+  <si>
+    <t>Rio Branco 93</t>
+  </si>
+  <si>
+    <t>2022-02-22</t>
+  </si>
+  <si>
+    <t>AXT</t>
+  </si>
+  <si>
+    <t>Cassio Hauck 70 · Sidnei 4 · Fischer 1</t>
+  </si>
+  <si>
+    <t>Chuy 65 · Rio Branco 8 · Rivera 2</t>
+  </si>
+  <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
+    <t>ATX | AXT</t>
+  </si>
+  <si>
+    <t>Mega Logistica</t>
+  </si>
+  <si>
+    <t>Paraguay HF 58 · Paraguay MS 2</t>
+  </si>
+  <si>
+    <t>Salto 60</t>
+  </si>
+  <si>
+    <t>Mega | Mega Logistica</t>
+  </si>
+  <si>
+    <t>Cmcn</t>
+  </si>
+  <si>
+    <t>Corupá 13 · Gilson 9 · Claudia 7 · Valdemar 5</t>
+  </si>
+  <si>
+    <t>Rivera 39</t>
+  </si>
+  <si>
+    <t>2019-01-09</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>CMCN</t>
+  </si>
+  <si>
+    <t>Osvelli</t>
+  </si>
+  <si>
+    <t>Corupá 10 · Claudia 10 · Valdemar 4 · Jaime 4</t>
+  </si>
+  <si>
+    <t>Rivera 35</t>
+  </si>
+  <si>
+    <t>2019-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>Osveli | Osvelii | Osvelli</t>
+  </si>
+  <si>
+    <t>G.S.C.S. PARAGUAY TTES.</t>
+  </si>
+  <si>
+    <t>Paraguay MS 18 · Paraguay HF 3</t>
+  </si>
+  <si>
+    <t>Salto 21</t>
+  </si>
+  <si>
+    <t>G.S.C.S. PARAGUAY TTES. | G.S.C.S. PARAGUAY TTES. S.R.L.</t>
+  </si>
+  <si>
+    <t>Compass</t>
+  </si>
+  <si>
+    <t>Paraguay DF 21</t>
+  </si>
+  <si>
+    <t>Compas | Compass</t>
+  </si>
+  <si>
+    <t>Dallog</t>
+  </si>
+  <si>
+    <t>BR SP 14 · BAHIA 2 · Jhony Viera 2 · Corupá 1</t>
+  </si>
+  <si>
+    <t>Rio Branco 20</t>
+  </si>
+  <si>
+    <t>2022-01-20</t>
+  </si>
+  <si>
+    <t>MARSO EMPRENDIMIENTOS S.R.L.</t>
+  </si>
+  <si>
+    <t>Paraguay AS 12</t>
+  </si>
+  <si>
+    <t>Salto 12</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>Jauser</t>
+  </si>
+  <si>
+    <t>Paraguay GM 4 · Paraguay DF 4 · Paraguay MS 2</t>
+  </si>
+  <si>
+    <t>Salto 10</t>
+  </si>
+  <si>
+    <t>Paraguay GM 7 · Paraguay DF 2</t>
+  </si>
+  <si>
+    <t>Salto 9</t>
+  </si>
+  <si>
+    <t>Lider Express</t>
+  </si>
+  <si>
+    <t>Paraguay MS 6 · Paraguay GM 2</t>
+  </si>
+  <si>
+    <t>Salto 8</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>Miro</t>
+  </si>
+  <si>
+    <t>Nordeste 7</t>
+  </si>
+  <si>
+    <t>Rio Branco 7</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-04-01</t>
+  </si>
+  <si>
+    <t>Agrologistica</t>
+  </si>
+  <si>
+    <t>Paraguay 6</t>
+  </si>
+  <si>
+    <t>Salto 6</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>2020-08-21</t>
+  </si>
+  <si>
+    <t>2020-07-26</t>
+  </si>
+  <si>
+    <t>2020-08-17</t>
+  </si>
+  <si>
+    <t>Milsiades</t>
+  </si>
+  <si>
+    <t>Paraguay MS 5</t>
+  </si>
+  <si>
+    <t>Salto 5</t>
+  </si>
+  <si>
+    <t>Nilton</t>
+  </si>
+  <si>
+    <t>Valdemar 2 · Banana Combinada 1 · Jhony Viera 1</t>
+  </si>
+  <si>
+    <t>Rio Branco 4</t>
+  </si>
+  <si>
+    <t>3G</t>
+  </si>
+  <si>
+    <t>Paraguay HF 4</t>
+  </si>
+  <si>
+    <t>Salto 4</t>
+  </si>
+  <si>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>OCH</t>
+  </si>
+  <si>
+    <t>Cassio Hauck 2 · Fischer 2</t>
+  </si>
+  <si>
+    <t>Brod</t>
+  </si>
+  <si>
+    <t>Jhony Viera 3 · Valdemar Ita 1</t>
+  </si>
+  <si>
+    <t>TEYU´I E HIJOS S.R.L.</t>
+  </si>
+  <si>
+    <t>Paraguay HF 3</t>
+  </si>
+  <si>
+    <t>Salto 3</t>
+  </si>
+  <si>
+    <t>Sergio Navas</t>
+  </si>
+  <si>
+    <t>BAHIA 1 · Gilson 1 · Jaime 1</t>
+  </si>
+  <si>
+    <t>Rivera 2 · Rio Branco 1</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>Sergio Nava | Sergio Navas</t>
+  </si>
+  <si>
+    <t>Agrovianbirc</t>
+  </si>
+  <si>
+    <t>BR SP 2 · AgroBianvirc 1</t>
+  </si>
+  <si>
+    <t>Rio Branco 3</t>
+  </si>
+  <si>
+    <t>2022-12-21</t>
+  </si>
+  <si>
+    <t>2023-06-28</t>
+  </si>
+  <si>
+    <t>Agrobianvirc | Agrovianbirc | BIANVIRC</t>
+  </si>
+  <si>
+    <t>Tahan</t>
+  </si>
+  <si>
+    <t>Paraguay SF 1 · Paraguay DF 1 · Paraguay GM 1</t>
+  </si>
+  <si>
+    <t>JC Transporte</t>
+  </si>
+  <si>
+    <t>Paraguay 3</t>
+  </si>
+  <si>
+    <t>2022-10-31</t>
+  </si>
+  <si>
+    <t>2022-11-04</t>
+  </si>
+  <si>
+    <t>Uniòn Sur</t>
+  </si>
+  <si>
+    <t>Paraguay 1</t>
+  </si>
+  <si>
+    <t>Salto 1</t>
+  </si>
+  <si>
+    <t>Kaipper</t>
+  </si>
+  <si>
+    <t>BR SP 1</t>
+  </si>
+  <si>
+    <t>Rio Branco 1</t>
+  </si>
+  <si>
+    <t>2022-11-03</t>
+  </si>
+  <si>
+    <t>Fartura</t>
+  </si>
+  <si>
+    <t>Valdemar 1</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>Roberdan</t>
+  </si>
+  <si>
+    <t>Sidnei 1</t>
+  </si>
+  <si>
+    <t>Rivera 1</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>Cargo Net</t>
+  </si>
+  <si>
+    <t>Paraguay MS 1</t>
+  </si>
+  <si>
+    <t>Aotrans</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>Benini</t>
+  </si>
+  <si>
+    <t>Benini 1</t>
+  </si>
+  <si>
+    <t>2023-06-13</t>
+  </si>
+  <si>
+    <t>productor</t>
+  </si>
+  <si>
+    <t>pais</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Otros</t>
+  </si>
+  <si>
+    <t>transportista principal</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>FG (38 %)</t>
+  </si>
+  <si>
+    <t>Cassio Hauck</t>
+  </si>
+  <si>
+    <t>AXT (37 %)</t>
+  </si>
+  <si>
+    <t>Valdemar</t>
+  </si>
+  <si>
+    <t>FG (82 %)</t>
+  </si>
+  <si>
+    <t>Jhony Viera</t>
+  </si>
+  <si>
+    <t>FG (77 %)</t>
+  </si>
+  <si>
+    <t>Corupá</t>
+  </si>
+  <si>
+    <t>FG (52 %)</t>
+  </si>
+  <si>
+    <t>Gilson</t>
+  </si>
+  <si>
+    <t>FG (56 %)</t>
+  </si>
+  <si>
+    <t>Paraguay HF</t>
+  </si>
+  <si>
+    <t>Mega Logistica (62 %)</t>
+  </si>
+  <si>
+    <t>Paraguay MS</t>
+  </si>
+  <si>
+    <t>G.S.C.S. PARAGUAY TTES. (42 %)</t>
+  </si>
+  <si>
+    <t>BAHIA</t>
+  </si>
+  <si>
+    <t>Gral (56 %)</t>
+  </si>
+  <si>
+    <t>Paraguay DF</t>
+  </si>
+  <si>
+    <t>Compass (57 %)</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>FG (46 %)</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>FG (62 %)</t>
+  </si>
+  <si>
+    <t>Osnildo Stein</t>
+  </si>
+  <si>
+    <t>Chabat (40 %)</t>
+  </si>
+  <si>
+    <t>Banana Combinada</t>
+  </si>
+  <si>
+    <t>Ivo Zimerman</t>
+  </si>
+  <si>
+    <t>Chabat (48 %)</t>
+  </si>
+  <si>
+    <t>Jorge Marangoni</t>
+  </si>
+  <si>
+    <t>Chabat (57 %)</t>
+  </si>
+  <si>
+    <t>Paraguay GM</t>
+  </si>
+  <si>
+    <t>Surcentral (41 %)</t>
+  </si>
+  <si>
+    <t>Marconi Kons</t>
+  </si>
+  <si>
+    <t>Chabat (53 %)</t>
+  </si>
+  <si>
+    <t>Paraguay AS</t>
+  </si>
+  <si>
+    <t>MARSO EMPRENDIMIENTOS S.R.L. (86 %)</t>
+  </si>
+  <si>
+    <t>Valdemar Ita</t>
+  </si>
+  <si>
+    <t>FG (71 %)</t>
+  </si>
+  <si>
+    <t>Wagner Schveitzer</t>
+  </si>
+  <si>
+    <t>Chabat (73 %)</t>
+  </si>
+  <si>
+    <t>Josemar Provesi</t>
+  </si>
+  <si>
+    <t>FG (40 %)</t>
+  </si>
+  <si>
+    <t>Furlani</t>
+  </si>
+  <si>
+    <t>Chabat (80 %)</t>
+  </si>
+  <si>
+    <t>Paraguay EC</t>
+  </si>
+  <si>
+    <t>(sin dato) (100 %)</t>
+  </si>
+  <si>
+    <t>Banana SP</t>
+  </si>
+  <si>
+    <t>Marvel (100 %)</t>
+  </si>
+  <si>
+    <t>Vitor</t>
+  </si>
+  <si>
+    <t>FG (88 %)</t>
+  </si>
+  <si>
+    <t>Tureck</t>
+  </si>
+  <si>
+    <t>Gral (83 %)</t>
+  </si>
+  <si>
+    <t>Chicolandia</t>
+  </si>
+  <si>
+    <t>Zanini (40 %)</t>
+  </si>
+  <si>
+    <t>João Claudio Winter</t>
+  </si>
+  <si>
+    <t>Chabat (100 %)</t>
+  </si>
+  <si>
+    <t>Zapellini</t>
+  </si>
+  <si>
+    <t>Amaro (75 %)</t>
+  </si>
+  <si>
+    <t>Shapo</t>
+  </si>
+  <si>
+    <t>FG (50 %)</t>
+  </si>
+  <si>
+    <t>Aldo Corupa</t>
+  </si>
+  <si>
+    <t>Chabat (50 %)</t>
+  </si>
+  <si>
+    <t>Corupa</t>
+  </si>
+  <si>
+    <t>FG (100 %)</t>
+  </si>
+  <si>
+    <t>Celso</t>
+  </si>
+  <si>
+    <t>Alexandre Wilbert</t>
+  </si>
+  <si>
+    <t>Banana MG</t>
+  </si>
+  <si>
+    <t>Zanini (100 %)</t>
+  </si>
+  <si>
+    <t>Marnei Meurer</t>
+  </si>
+  <si>
+    <t>Vinicios Bonkoski</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>anio</t>
+  </si>
+  <si>
+    <t>camiones</t>
+  </si>
+  <si>
+    <t>transportistas (con dato)</t>
+  </si>
+  <si>
+    <t>camiones sin dato</t>
+  </si>
+  <si>
+    <t>top1</t>
+  </si>
+  <si>
+    <t>top1 camiones</t>
+  </si>
+  <si>
+    <t>top1 pct</t>
+  </si>
+  <si>
+    <t>top2</t>
+  </si>
+  <si>
+    <t>top3</t>
+  </si>
+  <si>
+    <t>top3 pct</t>
+  </si>
+  <si>
+    <t>HHI</t>
+  </si>
+  <si>
+    <t>Silvio 153</t>
+  </si>
+  <si>
+    <t>Cmcn 31</t>
+  </si>
+  <si>
+    <t>Zanini 216</t>
+  </si>
+  <si>
+    <t>Alto Paraguay 29</t>
+  </si>
+  <si>
+    <t>Zanini 279</t>
+  </si>
+  <si>
+    <t>Gral 83</t>
+  </si>
+  <si>
+    <t>Silvio 217</t>
+  </si>
+  <si>
+    <t>Amaro 61</t>
+  </si>
+  <si>
+    <t>Silvio 167</t>
+  </si>
+  <si>
+    <t>Alto Paraguay 120</t>
+  </si>
+  <si>
+    <t>Silvio 147</t>
+  </si>
+  <si>
+    <t>Zanini 115</t>
+  </si>
+  <si>
+    <t>Zanini 122</t>
+  </si>
+  <si>
+    <t>Gral 87</t>
+  </si>
+  <si>
+    <t>Chabat 88</t>
+  </si>
+  <si>
+    <t>AXT 71</t>
   </si>
 </sst>
 </file>
@@ -10669,8 +11536,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
@@ -84413,6 +85283,6295 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AB41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.5941486358643" customWidth="1"/>
+    <col min="2" max="2" width="14.1785068511963" customWidth="1"/>
+    <col min="3" max="3" width="17.508864402771" customWidth="1"/>
+    <col min="4" max="4" width="12.2492847442627" customWidth="1"/>
+    <col min="5" max="5" width="12.2492847442627" customWidth="1"/>
+    <col min="6" max="6" width="12.2492847442627" customWidth="1"/>
+    <col min="7" max="7" width="12.2492847442627" customWidth="1"/>
+    <col min="8" max="8" width="12.2492847442627" customWidth="1"/>
+    <col min="9" max="9" width="12.2492847442627" customWidth="1"/>
+    <col min="10" max="10" width="12.2492847442627" customWidth="1"/>
+    <col min="11" max="11" width="12.2492847442627" customWidth="1"/>
+    <col min="12" max="12" width="11.3346652984619" customWidth="1"/>
+    <col min="13" max="13" width="11.3346652984619" customWidth="1"/>
+    <col min="14" max="14" width="13.5536937713623" customWidth="1"/>
+    <col min="15" max="15" width="17.422926902771" customWidth="1"/>
+    <col min="16" max="16" width="24.8882331848145" customWidth="1"/>
+    <col min="17" max="17" width="27.9942607879639" customWidth="1"/>
+    <col min="18" max="18" width="25.3833961486816" customWidth="1"/>
+    <col min="19" max="19" width="20.9013500213623" customWidth="1"/>
+    <col min="20" max="20" width="23.0467166900635" customWidth="1"/>
+    <col min="21" max="21" width="24.0718269348145" customWidth="1"/>
+    <col min="22" max="22" width="17.5815019607544" customWidth="1"/>
+    <col min="23" max="23" width="62.8876647949219" customWidth="1"/>
+    <col min="24" max="24" width="35.0930290222168" customWidth="1"/>
+    <col min="25" max="25" width="16.1041955947876" customWidth="1"/>
+    <col min="26" max="26" width="14.7609100341797" customWidth="1"/>
+    <col min="27" max="27" width="13.9526891708374" customWidth="1"/>
+    <col min="28" max="28" width="52.9322166442871" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="s">
+        <v>3533</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>3534</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>3535</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3536</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>3537</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>3538</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>3539</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>3540</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>3541</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>3542</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>3543</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>3544</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>3545</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>3546</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>3547</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>3548</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>3549</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>3550</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>3551</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>3552</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>3553</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>3554</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>3555</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>3556</v>
+      </c>
+      <c r="Y1" s="11" t="s">
+        <v>3557</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>3558</v>
+      </c>
+      <c r="AA1" s="11" t="s">
+        <v>3559</v>
+      </c>
+      <c r="AB1" s="11" t="s">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>3561</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3562</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1422</v>
+      </c>
+      <c r="D2" s="0">
+        <v>153</v>
+      </c>
+      <c r="E2" s="0">
+        <v>301</v>
+      </c>
+      <c r="F2" s="0">
+        <v>352</v>
+      </c>
+      <c r="G2" s="0">
+        <v>217</v>
+      </c>
+      <c r="H2" s="0">
+        <v>167</v>
+      </c>
+      <c r="I2" s="0">
+        <v>147</v>
+      </c>
+      <c r="J2" s="0">
+        <v>76</v>
+      </c>
+      <c r="K2" s="0">
+        <v>9</v>
+      </c>
+      <c r="L2" s="0">
+        <v>8.8</v>
+      </c>
+      <c r="M2" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="N2" s="0">
+        <v>2</v>
+      </c>
+      <c r="O2" s="0">
+        <v>0.1</v>
+      </c>
+      <c r="P2" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="0">
+        <v>1</v>
+      </c>
+      <c r="R2" s="0">
+        <v>4</v>
+      </c>
+      <c r="S2" s="0">
+        <v>9</v>
+      </c>
+      <c r="T2" s="0">
+        <v>45.5</v>
+      </c>
+      <c r="U2" s="0">
+        <v>976</v>
+      </c>
+      <c r="V2" s="0">
+        <v>21</v>
+      </c>
+      <c r="W2" s="0" t="s">
+        <v>3563</v>
+      </c>
+      <c r="X2" s="0" t="s">
+        <v>3564</v>
+      </c>
+      <c r="Y2" s="0" t="s">
+        <v>3565</v>
+      </c>
+      <c r="Z2" s="0" t="s">
+        <v>3252</v>
+      </c>
+      <c r="AA2" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB2" s="0" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>3568</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1386</v>
+      </c>
+      <c r="D3" s="0">
+        <v>233</v>
+      </c>
+      <c r="E3" s="0">
+        <v>216</v>
+      </c>
+      <c r="F3" s="0">
+        <v>279</v>
+      </c>
+      <c r="G3" s="0">
+        <v>241</v>
+      </c>
+      <c r="H3" s="0">
+        <v>175</v>
+      </c>
+      <c r="I3" s="0">
+        <v>115</v>
+      </c>
+      <c r="J3" s="0">
+        <v>122</v>
+      </c>
+      <c r="K3" s="0">
+        <v>5</v>
+      </c>
+      <c r="L3" s="0">
+        <v>14.2</v>
+      </c>
+      <c r="M3" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="N3" s="0">
+        <v>0</v>
+      </c>
+      <c r="O3" s="0">
+        <v>0</v>
+      </c>
+      <c r="P3" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="0">
+        <v>1</v>
+      </c>
+      <c r="R3" s="0">
+        <v>3</v>
+      </c>
+      <c r="S3" s="0">
+        <v>5</v>
+      </c>
+      <c r="T3" s="0">
+        <v>69.5</v>
+      </c>
+      <c r="U3" s="0">
+        <v>933</v>
+      </c>
+      <c r="V3" s="0">
+        <v>21</v>
+      </c>
+      <c r="W3" s="0" t="s">
+        <v>3570</v>
+      </c>
+      <c r="X3" s="0" t="s">
+        <v>3571</v>
+      </c>
+      <c r="Y3" s="0" t="s">
+        <v>3572</v>
+      </c>
+      <c r="Z3" s="0" t="s">
+        <v>2808</v>
+      </c>
+      <c r="AA3" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB3" s="0" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>3574</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C4" s="0">
+        <v>782</v>
+      </c>
+      <c r="D4" s="0">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0">
+        <v>0</v>
+      </c>
+      <c r="I4" s="0">
+        <v>188</v>
+      </c>
+      <c r="J4" s="0">
+        <v>369</v>
+      </c>
+      <c r="K4" s="0">
+        <v>225</v>
+      </c>
+      <c r="L4" s="0">
+        <v>42.8</v>
+      </c>
+      <c r="M4" s="0">
+        <v>36.6</v>
+      </c>
+      <c r="N4" s="0">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0">
+        <v>0</v>
+      </c>
+      <c r="P4" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="0">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0">
+        <v>3</v>
+      </c>
+      <c r="S4" s="0">
+        <v>4</v>
+      </c>
+      <c r="T4" s="0">
+        <v>66.6</v>
+      </c>
+      <c r="U4" s="0">
+        <v>1017</v>
+      </c>
+      <c r="V4" s="0">
+        <v>25</v>
+      </c>
+      <c r="W4" s="0" t="s">
+        <v>3575</v>
+      </c>
+      <c r="X4" s="0" t="s">
+        <v>3576</v>
+      </c>
+      <c r="Y4" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="Z4" s="0" t="s">
+        <v>3523</v>
+      </c>
+      <c r="AA4" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB4" s="0" t="s">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>3577</v>
+      </c>
+      <c r="C5" s="0">
+        <v>425</v>
+      </c>
+      <c r="D5" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5" s="0">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0">
+        <v>1</v>
+      </c>
+      <c r="H5" s="0">
+        <v>96</v>
+      </c>
+      <c r="I5" s="0">
+        <v>255</v>
+      </c>
+      <c r="J5" s="0">
+        <v>55</v>
+      </c>
+      <c r="K5" s="0">
+        <v>15</v>
+      </c>
+      <c r="L5" s="0">
+        <v>6.4</v>
+      </c>
+      <c r="M5" s="0">
+        <v>2.4</v>
+      </c>
+      <c r="N5" s="0">
+        <v>227</v>
+      </c>
+      <c r="O5" s="0">
+        <v>34.8</v>
+      </c>
+      <c r="P5" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="0">
+        <v>1</v>
+      </c>
+      <c r="R5" s="0">
+        <v>4</v>
+      </c>
+      <c r="S5" s="0">
+        <v>6</v>
+      </c>
+      <c r="T5" s="0">
+        <v>25.5</v>
+      </c>
+      <c r="U5" s="0">
+        <v>964</v>
+      </c>
+      <c r="V5" s="0">
+        <v>14</v>
+      </c>
+      <c r="W5" s="0" t="s">
+        <v>3578</v>
+      </c>
+      <c r="X5" s="0" t="s">
+        <v>3579</v>
+      </c>
+      <c r="Y5" s="0" t="s">
+        <v>3572</v>
+      </c>
+      <c r="Z5" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA5" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB5" s="0" t="s">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>3581</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C6" s="0">
+        <v>292</v>
+      </c>
+      <c r="D6" s="0">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0">
+        <v>39</v>
+      </c>
+      <c r="G6" s="0">
+        <v>61</v>
+      </c>
+      <c r="H6" s="0">
+        <v>22</v>
+      </c>
+      <c r="I6" s="0">
+        <v>52</v>
+      </c>
+      <c r="J6" s="0">
+        <v>60</v>
+      </c>
+      <c r="K6" s="0">
+        <v>58</v>
+      </c>
+      <c r="L6" s="0">
+        <v>7</v>
+      </c>
+      <c r="M6" s="0">
+        <v>9.4</v>
+      </c>
+      <c r="N6" s="0">
+        <v>0</v>
+      </c>
+      <c r="O6" s="0">
+        <v>0</v>
+      </c>
+      <c r="P6" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="0">
+        <v>1</v>
+      </c>
+      <c r="R6" s="0">
+        <v>3</v>
+      </c>
+      <c r="S6" s="0">
+        <v>5</v>
+      </c>
+      <c r="T6" s="0">
+        <v>63</v>
+      </c>
+      <c r="U6" s="0">
+        <v>998</v>
+      </c>
+      <c r="V6" s="0">
+        <v>22</v>
+      </c>
+      <c r="W6" s="0" t="s">
+        <v>3582</v>
+      </c>
+      <c r="X6" s="0" t="s">
+        <v>3583</v>
+      </c>
+      <c r="Y6" s="0" t="s">
+        <v>3584</v>
+      </c>
+      <c r="Z6" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA6" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB6" s="0" t="s">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>3585</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C7" s="0">
+        <v>250</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0">
+        <v>29</v>
+      </c>
+      <c r="F7" s="0">
+        <v>47</v>
+      </c>
+      <c r="G7" s="0">
+        <v>54</v>
+      </c>
+      <c r="H7" s="0">
+        <v>120</v>
+      </c>
+      <c r="I7" s="0">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0">
+        <v>0</v>
+      </c>
+      <c r="N7" s="0">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0">
+        <v>0</v>
+      </c>
+      <c r="P7" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="0">
+        <v>1</v>
+      </c>
+      <c r="R7" s="0">
+        <v>4</v>
+      </c>
+      <c r="S7" s="0">
+        <v>7</v>
+      </c>
+      <c r="T7" s="0">
+        <v>25.2</v>
+      </c>
+      <c r="U7" s="0">
+        <v>1350</v>
+      </c>
+      <c r="V7" s="0">
+        <v>2</v>
+      </c>
+      <c r="W7" s="0" t="s">
+        <v>3587</v>
+      </c>
+      <c r="X7" s="0" t="s">
+        <v>3588</v>
+      </c>
+      <c r="Y7" s="0" t="s">
+        <v>3589</v>
+      </c>
+      <c r="Z7" s="0" t="s">
+        <v>3590</v>
+      </c>
+      <c r="AA7" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB7" s="0" t="s">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>3592</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C8" s="0">
+        <v>209</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0">
+        <v>8</v>
+      </c>
+      <c r="F8" s="0">
+        <v>83</v>
+      </c>
+      <c r="G8" s="0">
+        <v>31</v>
+      </c>
+      <c r="H8" s="0">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0">
+        <v>87</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0">
+        <v>10.1</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0">
+        <v>0</v>
+      </c>
+      <c r="O8" s="0">
+        <v>0</v>
+      </c>
+      <c r="P8" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>1</v>
+      </c>
+      <c r="R8" s="0">
+        <v>3</v>
+      </c>
+      <c r="S8" s="0">
+        <v>6</v>
+      </c>
+      <c r="T8" s="0">
+        <v>53.6</v>
+      </c>
+      <c r="U8" s="0">
+        <v>923</v>
+      </c>
+      <c r="V8" s="0">
+        <v>15</v>
+      </c>
+      <c r="W8" s="0" t="s">
+        <v>3593</v>
+      </c>
+      <c r="X8" s="0" t="s">
+        <v>3594</v>
+      </c>
+      <c r="Y8" s="0" t="s">
+        <v>3595</v>
+      </c>
+      <c r="Z8" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA8" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB8" s="0" t="s">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>3596</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C9" s="0">
+        <v>151</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0">
+        <v>5</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0">
+        <v>58</v>
+      </c>
+      <c r="K9" s="0">
+        <v>88</v>
+      </c>
+      <c r="L9" s="0">
+        <v>6.7</v>
+      </c>
+      <c r="M9" s="0">
+        <v>14.3</v>
+      </c>
+      <c r="N9" s="0">
+        <v>0</v>
+      </c>
+      <c r="O9" s="0">
+        <v>0</v>
+      </c>
+      <c r="P9" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="0">
+        <v>1</v>
+      </c>
+      <c r="R9" s="0">
+        <v>3</v>
+      </c>
+      <c r="S9" s="0">
+        <v>4</v>
+      </c>
+      <c r="T9" s="0">
+        <v>64.2</v>
+      </c>
+      <c r="U9" s="0">
+        <v>993</v>
+      </c>
+      <c r="V9" s="0">
+        <v>21</v>
+      </c>
+      <c r="W9" s="0" t="s">
+        <v>3597</v>
+      </c>
+      <c r="X9" s="0" t="s">
+        <v>3598</v>
+      </c>
+      <c r="Y9" s="0" t="s">
+        <v>3599</v>
+      </c>
+      <c r="Z9" s="0" t="s">
+        <v>3523</v>
+      </c>
+      <c r="AA9" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB9" s="0" t="s">
+        <v>3596</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>3600</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C10" s="0">
+        <v>93</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0">
+        <v>67</v>
+      </c>
+      <c r="J10" s="0">
+        <v>25</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0">
+        <v>2.9</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0">
+        <v>0</v>
+      </c>
+      <c r="P10" s="0">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="0">
+        <v>1</v>
+      </c>
+      <c r="R10" s="0">
+        <v>7</v>
+      </c>
+      <c r="S10" s="0">
+        <v>9</v>
+      </c>
+      <c r="T10" s="0">
+        <v>3.2</v>
+      </c>
+      <c r="U10" s="0">
+        <v>934</v>
+      </c>
+      <c r="V10" s="0">
+        <v>7</v>
+      </c>
+      <c r="W10" s="0" t="s">
+        <v>3601</v>
+      </c>
+      <c r="X10" s="0" t="s">
+        <v>3602</v>
+      </c>
+      <c r="Y10" s="0" t="s">
+        <v>3603</v>
+      </c>
+      <c r="Z10" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA10" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB10" s="0" t="s">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>3604</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C11" s="0">
+        <v>75</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0">
+        <v>4</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" s="0">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0">
+        <v>71</v>
+      </c>
+      <c r="L11" s="0">
+        <v>0</v>
+      </c>
+      <c r="M11" s="0">
+        <v>11.6</v>
+      </c>
+      <c r="N11" s="0">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0">
+        <v>0</v>
+      </c>
+      <c r="P11" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="0">
+        <v>1</v>
+      </c>
+      <c r="R11" s="0">
+        <v>3</v>
+      </c>
+      <c r="S11" s="0">
+        <v>4</v>
+      </c>
+      <c r="T11" s="0">
+        <v>66.7</v>
+      </c>
+      <c r="U11" s="0">
+        <v>939</v>
+      </c>
+      <c r="V11" s="0">
+        <v>3</v>
+      </c>
+      <c r="W11" s="0" t="s">
+        <v>3605</v>
+      </c>
+      <c r="X11" s="0" t="s">
+        <v>3606</v>
+      </c>
+      <c r="Y11" s="0" t="s">
+        <v>3607</v>
+      </c>
+      <c r="Z11" s="0" t="s">
+        <v>3523</v>
+      </c>
+      <c r="AA11" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB11" s="0" t="s">
+        <v>3608</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>3609</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C12" s="0">
+        <v>60</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0">
+        <v>0</v>
+      </c>
+      <c r="G12" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" s="0">
+        <v>0</v>
+      </c>
+      <c r="I12" s="0">
+        <v>0</v>
+      </c>
+      <c r="J12" s="0">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0">
+        <v>60</v>
+      </c>
+      <c r="L12" s="0">
+        <v>0</v>
+      </c>
+      <c r="M12" s="0">
+        <v>9.8</v>
+      </c>
+      <c r="N12" s="0">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0">
+        <v>0</v>
+      </c>
+      <c r="P12" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="0">
+        <v>1</v>
+      </c>
+      <c r="R12" s="0">
+        <v>4</v>
+      </c>
+      <c r="S12" s="0">
+        <v>4</v>
+      </c>
+      <c r="T12" s="0">
+        <v>45</v>
+      </c>
+      <c r="U12" s="0">
+        <v>975</v>
+      </c>
+      <c r="V12" s="0">
+        <v>2</v>
+      </c>
+      <c r="W12" s="0" t="s">
+        <v>3610</v>
+      </c>
+      <c r="X12" s="0" t="s">
+        <v>3611</v>
+      </c>
+      <c r="Y12" s="0" t="s">
+        <v>2855</v>
+      </c>
+      <c r="Z12" s="0" t="s">
+        <v>3454</v>
+      </c>
+      <c r="AA12" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB12" s="0" t="s">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>3613</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C13" s="0">
+        <v>39</v>
+      </c>
+      <c r="D13" s="0">
+        <v>31</v>
+      </c>
+      <c r="E13" s="0">
+        <v>8</v>
+      </c>
+      <c r="F13" s="0">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" s="0">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0">
+        <v>0</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0">
+        <v>0</v>
+      </c>
+      <c r="L13" s="0">
+        <v>0</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0">
+        <v>0</v>
+      </c>
+      <c r="O13" s="0">
+        <v>0</v>
+      </c>
+      <c r="P13" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="0">
+        <v>1</v>
+      </c>
+      <c r="R13" s="0">
+        <v>3</v>
+      </c>
+      <c r="S13" s="0">
+        <v>5</v>
+      </c>
+      <c r="T13" s="0">
+        <v>53.8</v>
+      </c>
+      <c r="U13" s="0">
+        <v>928</v>
+      </c>
+      <c r="V13" s="0">
+        <v>6</v>
+      </c>
+      <c r="W13" s="0" t="s">
+        <v>3614</v>
+      </c>
+      <c r="X13" s="0" t="s">
+        <v>3615</v>
+      </c>
+      <c r="Y13" s="0" t="s">
+        <v>3616</v>
+      </c>
+      <c r="Z13" s="0" t="s">
+        <v>3617</v>
+      </c>
+      <c r="AA13" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB13" s="0" t="s">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>3619</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C14" s="0">
+        <v>35</v>
+      </c>
+      <c r="D14" s="0">
+        <v>27</v>
+      </c>
+      <c r="E14" s="0">
+        <v>8</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0">
+        <v>0</v>
+      </c>
+      <c r="P14" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>1</v>
+      </c>
+      <c r="R14" s="0">
+        <v>3</v>
+      </c>
+      <c r="S14" s="0">
+        <v>5</v>
+      </c>
+      <c r="T14" s="0">
+        <v>65.7</v>
+      </c>
+      <c r="U14" s="0">
+        <v>930</v>
+      </c>
+      <c r="V14" s="0">
+        <v>7</v>
+      </c>
+      <c r="W14" s="0" t="s">
+        <v>3620</v>
+      </c>
+      <c r="X14" s="0" t="s">
+        <v>3621</v>
+      </c>
+      <c r="Y14" s="0" t="s">
+        <v>3622</v>
+      </c>
+      <c r="Z14" s="0" t="s">
+        <v>3623</v>
+      </c>
+      <c r="AA14" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB14" s="0" t="s">
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>3625</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C15" s="0">
+        <v>21</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" s="0">
+        <v>0</v>
+      </c>
+      <c r="I15" s="0">
+        <v>0</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0">
+        <v>21</v>
+      </c>
+      <c r="L15" s="0">
+        <v>0</v>
+      </c>
+      <c r="M15" s="0">
+        <v>3.4</v>
+      </c>
+      <c r="N15" s="0">
+        <v>0</v>
+      </c>
+      <c r="O15" s="0">
+        <v>0</v>
+      </c>
+      <c r="P15" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="0">
+        <v>1</v>
+      </c>
+      <c r="R15" s="0">
+        <v>4</v>
+      </c>
+      <c r="S15" s="0">
+        <v>5</v>
+      </c>
+      <c r="T15" s="0">
+        <v>42.9</v>
+      </c>
+      <c r="U15" s="0">
+        <v>981</v>
+      </c>
+      <c r="V15" s="0">
+        <v>2</v>
+      </c>
+      <c r="W15" s="0" t="s">
+        <v>3626</v>
+      </c>
+      <c r="X15" s="0" t="s">
+        <v>3627</v>
+      </c>
+      <c r="Y15" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z15" s="0" t="s">
+        <v>3523</v>
+      </c>
+      <c r="AA15" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB15" s="0" t="s">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>3629</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C16" s="0">
+        <v>21</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0">
+        <v>0</v>
+      </c>
+      <c r="G16" s="0">
+        <v>0</v>
+      </c>
+      <c r="H16" s="0">
+        <v>0</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0">
+        <v>21</v>
+      </c>
+      <c r="L16" s="0">
+        <v>0</v>
+      </c>
+      <c r="M16" s="0">
+        <v>3.4</v>
+      </c>
+      <c r="N16" s="0">
+        <v>0</v>
+      </c>
+      <c r="O16" s="0">
+        <v>0</v>
+      </c>
+      <c r="P16" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="0">
+        <v>1</v>
+      </c>
+      <c r="R16" s="0">
+        <v>3</v>
+      </c>
+      <c r="S16" s="0">
+        <v>4</v>
+      </c>
+      <c r="T16" s="0">
+        <v>52.4</v>
+      </c>
+      <c r="U16" s="0">
+        <v>981</v>
+      </c>
+      <c r="V16" s="0">
+        <v>1</v>
+      </c>
+      <c r="W16" s="0" t="s">
+        <v>3630</v>
+      </c>
+      <c r="X16" s="0" t="s">
+        <v>3627</v>
+      </c>
+      <c r="Y16" s="0" t="s">
+        <v>2812</v>
+      </c>
+      <c r="Z16" s="0" t="s">
+        <v>3523</v>
+      </c>
+      <c r="AA16" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB16" s="0" t="s">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>3632</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C17" s="0">
+        <v>20</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0">
+        <v>17</v>
+      </c>
+      <c r="H17" s="0">
+        <v>1</v>
+      </c>
+      <c r="I17" s="0">
+        <v>2</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0">
+        <v>0</v>
+      </c>
+      <c r="L17" s="0">
+        <v>0</v>
+      </c>
+      <c r="M17" s="0">
+        <v>0</v>
+      </c>
+      <c r="N17" s="0">
+        <v>0</v>
+      </c>
+      <c r="O17" s="0">
+        <v>0</v>
+      </c>
+      <c r="P17" s="0">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="0">
+        <v>1</v>
+      </c>
+      <c r="R17" s="0">
+        <v>6</v>
+      </c>
+      <c r="S17" s="0">
+        <v>9</v>
+      </c>
+      <c r="T17" s="0">
+        <v>30</v>
+      </c>
+      <c r="U17" s="0">
+        <v>931</v>
+      </c>
+      <c r="V17" s="0">
+        <v>5</v>
+      </c>
+      <c r="W17" s="0" t="s">
+        <v>3633</v>
+      </c>
+      <c r="X17" s="0" t="s">
+        <v>3634</v>
+      </c>
+      <c r="Y17" s="0" t="s">
+        <v>3635</v>
+      </c>
+      <c r="Z17" s="0" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AA17" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB17" s="0" t="s">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>3636</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C18" s="0">
+        <v>12</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0">
+        <v>0</v>
+      </c>
+      <c r="H18" s="0">
+        <v>0</v>
+      </c>
+      <c r="I18" s="0">
+        <v>0</v>
+      </c>
+      <c r="J18" s="0">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0">
+        <v>12</v>
+      </c>
+      <c r="L18" s="0">
+        <v>0</v>
+      </c>
+      <c r="M18" s="0">
+        <v>2</v>
+      </c>
+      <c r="N18" s="0">
+        <v>0</v>
+      </c>
+      <c r="O18" s="0">
+        <v>0</v>
+      </c>
+      <c r="P18" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="0">
+        <v>1</v>
+      </c>
+      <c r="R18" s="0">
+        <v>3</v>
+      </c>
+      <c r="S18" s="0">
+        <v>4</v>
+      </c>
+      <c r="T18" s="0">
+        <v>83.3</v>
+      </c>
+      <c r="U18" s="0">
+        <v>984</v>
+      </c>
+      <c r="V18" s="0">
+        <v>1</v>
+      </c>
+      <c r="W18" s="0" t="s">
+        <v>3637</v>
+      </c>
+      <c r="X18" s="0" t="s">
+        <v>3638</v>
+      </c>
+      <c r="Y18" s="0" t="s">
+        <v>3639</v>
+      </c>
+      <c r="Z18" s="0" t="s">
+        <v>3522</v>
+      </c>
+      <c r="AA18" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB18" s="0" t="s">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>3640</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C19" s="0">
+        <v>10</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" s="0">
+        <v>0</v>
+      </c>
+      <c r="I19" s="0">
+        <v>8</v>
+      </c>
+      <c r="J19" s="0">
+        <v>1</v>
+      </c>
+      <c r="K19" s="0">
+        <v>1</v>
+      </c>
+      <c r="L19" s="0">
+        <v>0.1</v>
+      </c>
+      <c r="M19" s="0">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="0">
+        <v>0</v>
+      </c>
+      <c r="O19" s="0">
+        <v>0</v>
+      </c>
+      <c r="P19" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="0">
+        <v>1</v>
+      </c>
+      <c r="R19" s="0">
+        <v>4</v>
+      </c>
+      <c r="S19" s="0">
+        <v>7</v>
+      </c>
+      <c r="T19" s="0">
+        <v>20</v>
+      </c>
+      <c r="U19" s="0">
+        <v>978</v>
+      </c>
+      <c r="V19" s="0">
+        <v>3</v>
+      </c>
+      <c r="W19" s="0" t="s">
+        <v>3641</v>
+      </c>
+      <c r="X19" s="0" t="s">
+        <v>3642</v>
+      </c>
+      <c r="Y19" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="Z19" s="0" t="s">
+        <v>3390</v>
+      </c>
+      <c r="AA19" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB19" s="0" t="s">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C20" s="0">
+        <v>9</v>
+      </c>
+      <c r="D20" s="0">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0">
+        <v>0</v>
+      </c>
+      <c r="H20" s="0">
+        <v>0</v>
+      </c>
+      <c r="I20" s="0">
+        <v>0</v>
+      </c>
+      <c r="J20" s="0">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0">
+        <v>9</v>
+      </c>
+      <c r="L20" s="0">
+        <v>0</v>
+      </c>
+      <c r="M20" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="N20" s="0">
+        <v>0</v>
+      </c>
+      <c r="O20" s="0">
+        <v>0</v>
+      </c>
+      <c r="P20" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="0">
+        <v>1</v>
+      </c>
+      <c r="R20" s="0">
+        <v>4</v>
+      </c>
+      <c r="S20" s="0">
+        <v>5</v>
+      </c>
+      <c r="T20" s="0">
+        <v>11.1</v>
+      </c>
+      <c r="U20" s="0">
+        <v>973</v>
+      </c>
+      <c r="V20" s="0">
+        <v>2</v>
+      </c>
+      <c r="W20" s="0" t="s">
+        <v>3643</v>
+      </c>
+      <c r="X20" s="0" t="s">
+        <v>3644</v>
+      </c>
+      <c r="Y20" s="0" t="s">
+        <v>2704</v>
+      </c>
+      <c r="Z20" s="0" t="s">
+        <v>3070</v>
+      </c>
+      <c r="AA20" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB20" s="0" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>3645</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C21" s="0">
+        <v>8</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0</v>
+      </c>
+      <c r="F21" s="0">
+        <v>0</v>
+      </c>
+      <c r="G21" s="0">
+        <v>0</v>
+      </c>
+      <c r="H21" s="0">
+        <v>0</v>
+      </c>
+      <c r="I21" s="0">
+        <v>0</v>
+      </c>
+      <c r="J21" s="0">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0">
+        <v>8</v>
+      </c>
+      <c r="L21" s="0">
+        <v>0</v>
+      </c>
+      <c r="M21" s="0">
+        <v>1.3</v>
+      </c>
+      <c r="N21" s="0">
+        <v>0</v>
+      </c>
+      <c r="O21" s="0">
+        <v>0</v>
+      </c>
+      <c r="P21" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="0">
+        <v>1</v>
+      </c>
+      <c r="R21" s="0">
+        <v>4</v>
+      </c>
+      <c r="S21" s="0">
+        <v>5</v>
+      </c>
+      <c r="T21" s="0">
+        <v>25</v>
+      </c>
+      <c r="U21" s="0">
+        <v>980</v>
+      </c>
+      <c r="V21" s="0">
+        <v>2</v>
+      </c>
+      <c r="W21" s="0" t="s">
+        <v>3646</v>
+      </c>
+      <c r="X21" s="0" t="s">
+        <v>3647</v>
+      </c>
+      <c r="Y21" s="0" t="s">
+        <v>3302</v>
+      </c>
+      <c r="Z21" s="0" t="s">
+        <v>3648</v>
+      </c>
+      <c r="AA21" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB21" s="0" t="s">
+        <v>3645</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>3649</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C22" s="0">
+        <v>7</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0</v>
+      </c>
+      <c r="E22" s="0">
+        <v>0</v>
+      </c>
+      <c r="F22" s="0">
+        <v>7</v>
+      </c>
+      <c r="G22" s="0">
+        <v>0</v>
+      </c>
+      <c r="H22" s="0">
+        <v>0</v>
+      </c>
+      <c r="I22" s="0">
+        <v>0</v>
+      </c>
+      <c r="J22" s="0">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0">
+        <v>0</v>
+      </c>
+      <c r="L22" s="0">
+        <v>0</v>
+      </c>
+      <c r="M22" s="0">
+        <v>0</v>
+      </c>
+      <c r="N22" s="0">
+        <v>0</v>
+      </c>
+      <c r="O22" s="0">
+        <v>0</v>
+      </c>
+      <c r="P22" s="0">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="0">
+        <v>1</v>
+      </c>
+      <c r="R22" s="0">
+        <v>9</v>
+      </c>
+      <c r="S22" s="0">
+        <v>12</v>
+      </c>
+      <c r="T22" s="0">
+        <v>0</v>
+      </c>
+      <c r="U22" s="0">
+        <v>1152</v>
+      </c>
+      <c r="V22" s="0">
+        <v>1</v>
+      </c>
+      <c r="W22" s="0" t="s">
+        <v>3650</v>
+      </c>
+      <c r="X22" s="0" t="s">
+        <v>3651</v>
+      </c>
+      <c r="Y22" s="0" t="s">
+        <v>3652</v>
+      </c>
+      <c r="Z22" s="0" t="s">
+        <v>3653</v>
+      </c>
+      <c r="AA22" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB22" s="0" t="s">
+        <v>3649</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>3654</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C23" s="0">
+        <v>6</v>
+      </c>
+      <c r="D23" s="0">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0">
+        <v>6</v>
+      </c>
+      <c r="F23" s="0">
+        <v>0</v>
+      </c>
+      <c r="G23" s="0">
+        <v>0</v>
+      </c>
+      <c r="H23" s="0">
+        <v>0</v>
+      </c>
+      <c r="I23" s="0">
+        <v>0</v>
+      </c>
+      <c r="J23" s="0">
+        <v>0</v>
+      </c>
+      <c r="K23" s="0">
+        <v>0</v>
+      </c>
+      <c r="L23" s="0">
+        <v>0</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0</v>
+      </c>
+      <c r="N23" s="0">
+        <v>0</v>
+      </c>
+      <c r="O23" s="0">
+        <v>0</v>
+      </c>
+      <c r="P23" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="0">
+        <v>1</v>
+      </c>
+      <c r="R23" s="0">
+        <v>4</v>
+      </c>
+      <c r="S23" s="0">
+        <v>6</v>
+      </c>
+      <c r="T23" s="0">
+        <v>33.3</v>
+      </c>
+      <c r="U23" s="0">
+        <v>991</v>
+      </c>
+      <c r="V23" s="0">
+        <v>1</v>
+      </c>
+      <c r="W23" s="0" t="s">
+        <v>3655</v>
+      </c>
+      <c r="X23" s="0" t="s">
+        <v>3656</v>
+      </c>
+      <c r="Y23" s="0" t="s">
+        <v>3657</v>
+      </c>
+      <c r="Z23" s="0" t="s">
+        <v>3658</v>
+      </c>
+      <c r="AA23" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB23" s="0" t="s">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C24" s="0">
+        <v>6</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0">
+        <v>6</v>
+      </c>
+      <c r="F24" s="0">
+        <v>0</v>
+      </c>
+      <c r="G24" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" s="0">
+        <v>0</v>
+      </c>
+      <c r="I24" s="0">
+        <v>0</v>
+      </c>
+      <c r="J24" s="0">
+        <v>0</v>
+      </c>
+      <c r="K24" s="0">
+        <v>0</v>
+      </c>
+      <c r="L24" s="0">
+        <v>0</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0</v>
+      </c>
+      <c r="N24" s="0">
+        <v>0</v>
+      </c>
+      <c r="O24" s="0">
+        <v>0</v>
+      </c>
+      <c r="P24" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="0">
+        <v>2</v>
+      </c>
+      <c r="R24" s="0">
+        <v>5</v>
+      </c>
+      <c r="S24" s="0">
+        <v>6</v>
+      </c>
+      <c r="T24" s="0">
+        <v>16.7</v>
+      </c>
+      <c r="U24" s="0">
+        <v>990</v>
+      </c>
+      <c r="V24" s="0">
+        <v>1</v>
+      </c>
+      <c r="W24" s="0" t="s">
+        <v>3655</v>
+      </c>
+      <c r="X24" s="0" t="s">
+        <v>3656</v>
+      </c>
+      <c r="Y24" s="0" t="s">
+        <v>3659</v>
+      </c>
+      <c r="Z24" s="0" t="s">
+        <v>3660</v>
+      </c>
+      <c r="AA24" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB24" s="0" t="s">
+        <v>3054</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>3661</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C25" s="0">
+        <v>5</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0">
+        <v>0</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0</v>
+      </c>
+      <c r="I25" s="0">
+        <v>0</v>
+      </c>
+      <c r="J25" s="0">
+        <v>5</v>
+      </c>
+      <c r="K25" s="0">
+        <v>0</v>
+      </c>
+      <c r="L25" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0</v>
+      </c>
+      <c r="N25" s="0">
+        <v>0</v>
+      </c>
+      <c r="O25" s="0">
+        <v>0</v>
+      </c>
+      <c r="P25" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="0">
+        <v>1</v>
+      </c>
+      <c r="R25" s="0">
+        <v>4</v>
+      </c>
+      <c r="S25" s="0">
+        <v>7</v>
+      </c>
+      <c r="T25" s="0">
+        <v>20</v>
+      </c>
+      <c r="U25" s="0">
+        <v>968</v>
+      </c>
+      <c r="V25" s="0">
+        <v>1</v>
+      </c>
+      <c r="W25" s="0" t="s">
+        <v>3662</v>
+      </c>
+      <c r="X25" s="0" t="s">
+        <v>3663</v>
+      </c>
+      <c r="Y25" s="0" t="s">
+        <v>1691</v>
+      </c>
+      <c r="Z25" s="0" t="s">
+        <v>1765</v>
+      </c>
+      <c r="AA25" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB25" s="0" t="s">
+        <v>3661</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>3664</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C26" s="0">
+        <v>4</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0">
+        <v>0</v>
+      </c>
+      <c r="G26" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0">
+        <v>0</v>
+      </c>
+      <c r="J26" s="0">
+        <v>4</v>
+      </c>
+      <c r="K26" s="0">
+        <v>0</v>
+      </c>
+      <c r="L26" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0</v>
+      </c>
+      <c r="N26" s="0">
+        <v>0</v>
+      </c>
+      <c r="O26" s="0">
+        <v>0</v>
+      </c>
+      <c r="P26" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="0">
+        <v>1</v>
+      </c>
+      <c r="R26" s="0">
+        <v>3</v>
+      </c>
+      <c r="S26" s="0">
+        <v>4</v>
+      </c>
+      <c r="T26" s="0">
+        <v>75</v>
+      </c>
+      <c r="U26" s="0">
+        <v>990</v>
+      </c>
+      <c r="V26" s="0">
+        <v>3</v>
+      </c>
+      <c r="W26" s="0" t="s">
+        <v>3665</v>
+      </c>
+      <c r="X26" s="0" t="s">
+        <v>3666</v>
+      </c>
+      <c r="Y26" s="0" t="s">
+        <v>1844</v>
+      </c>
+      <c r="Z26" s="0" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AA26" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB26" s="0" t="s">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>3667</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C27" s="0">
+        <v>4</v>
+      </c>
+      <c r="D27" s="0">
+        <v>0</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0">
+        <v>0</v>
+      </c>
+      <c r="G27" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0</v>
+      </c>
+      <c r="I27" s="0">
+        <v>0</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0</v>
+      </c>
+      <c r="K27" s="0">
+        <v>4</v>
+      </c>
+      <c r="L27" s="0">
+        <v>0</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="N27" s="0">
+        <v>0</v>
+      </c>
+      <c r="O27" s="0">
+        <v>0</v>
+      </c>
+      <c r="P27" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>1</v>
+      </c>
+      <c r="R27" s="0">
+        <v>3</v>
+      </c>
+      <c r="S27" s="0">
+        <v>4</v>
+      </c>
+      <c r="T27" s="0">
+        <v>75</v>
+      </c>
+      <c r="U27" s="0">
+        <v>981</v>
+      </c>
+      <c r="V27" s="0">
+        <v>1</v>
+      </c>
+      <c r="W27" s="0" t="s">
+        <v>3668</v>
+      </c>
+      <c r="X27" s="0" t="s">
+        <v>3669</v>
+      </c>
+      <c r="Y27" s="0" t="s">
+        <v>3670</v>
+      </c>
+      <c r="Z27" s="0" t="s">
+        <v>2682</v>
+      </c>
+      <c r="AA27" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB27" s="0" t="s">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>3671</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C28" s="0">
+        <v>4</v>
+      </c>
+      <c r="D28" s="0">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0</v>
+      </c>
+      <c r="F28" s="0">
+        <v>0</v>
+      </c>
+      <c r="G28" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0</v>
+      </c>
+      <c r="I28" s="0">
+        <v>0</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0</v>
+      </c>
+      <c r="K28" s="0">
+        <v>4</v>
+      </c>
+      <c r="L28" s="0">
+        <v>0</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="N28" s="0">
+        <v>0</v>
+      </c>
+      <c r="O28" s="0">
+        <v>0</v>
+      </c>
+      <c r="P28" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>1</v>
+      </c>
+      <c r="R28" s="0">
+        <v>4</v>
+      </c>
+      <c r="S28" s="0">
+        <v>5</v>
+      </c>
+      <c r="T28" s="0">
+        <v>50</v>
+      </c>
+      <c r="U28" s="0">
+        <v>1008</v>
+      </c>
+      <c r="V28" s="0">
+        <v>2</v>
+      </c>
+      <c r="W28" s="0" t="s">
+        <v>3672</v>
+      </c>
+      <c r="X28" s="0" t="s">
+        <v>3666</v>
+      </c>
+      <c r="Y28" s="0" t="s">
+        <v>2849</v>
+      </c>
+      <c r="Z28" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA28" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB28" s="0" t="s">
+        <v>3671</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C29" s="0">
+        <v>4</v>
+      </c>
+      <c r="D29" s="0">
+        <v>0</v>
+      </c>
+      <c r="E29" s="0">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0">
+        <v>0</v>
+      </c>
+      <c r="G29" s="0">
+        <v>0</v>
+      </c>
+      <c r="H29" s="0">
+        <v>0</v>
+      </c>
+      <c r="I29" s="0">
+        <v>4</v>
+      </c>
+      <c r="J29" s="0">
+        <v>0</v>
+      </c>
+      <c r="K29" s="0">
+        <v>0</v>
+      </c>
+      <c r="L29" s="0">
+        <v>0</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0</v>
+      </c>
+      <c r="N29" s="0">
+        <v>0</v>
+      </c>
+      <c r="O29" s="0">
+        <v>0</v>
+      </c>
+      <c r="P29" s="0">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="0">
+        <v>1</v>
+      </c>
+      <c r="R29" s="0">
+        <v>4</v>
+      </c>
+      <c r="S29" s="0">
+        <v>6</v>
+      </c>
+      <c r="T29" s="0">
+        <v>25</v>
+      </c>
+      <c r="U29" s="0">
+        <v>990</v>
+      </c>
+      <c r="V29" s="0">
+        <v>2</v>
+      </c>
+      <c r="W29" s="0" t="s">
+        <v>3674</v>
+      </c>
+      <c r="X29" s="0" t="s">
+        <v>3666</v>
+      </c>
+      <c r="Y29" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z29" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="AA29" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB29" s="0" t="s">
+        <v>3673</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>3675</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C30" s="0">
+        <v>3</v>
+      </c>
+      <c r="D30" s="0">
+        <v>0</v>
+      </c>
+      <c r="E30" s="0">
+        <v>0</v>
+      </c>
+      <c r="F30" s="0">
+        <v>0</v>
+      </c>
+      <c r="G30" s="0">
+        <v>0</v>
+      </c>
+      <c r="H30" s="0">
+        <v>0</v>
+      </c>
+      <c r="I30" s="0">
+        <v>0</v>
+      </c>
+      <c r="J30" s="0">
+        <v>0</v>
+      </c>
+      <c r="K30" s="0">
+        <v>3</v>
+      </c>
+      <c r="L30" s="0">
+        <v>0</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="N30" s="0">
+        <v>0</v>
+      </c>
+      <c r="O30" s="0">
+        <v>0</v>
+      </c>
+      <c r="P30" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="0">
+        <v>1</v>
+      </c>
+      <c r="R30" s="0">
+        <v>3</v>
+      </c>
+      <c r="S30" s="0">
+        <v>5</v>
+      </c>
+      <c r="T30" s="0">
+        <v>66.7</v>
+      </c>
+      <c r="U30" s="0">
+        <v>980</v>
+      </c>
+      <c r="V30" s="0">
+        <v>1</v>
+      </c>
+      <c r="W30" s="0" t="s">
+        <v>3676</v>
+      </c>
+      <c r="X30" s="0" t="s">
+        <v>3677</v>
+      </c>
+      <c r="Y30" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z30" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA30" s="0" t="s">
+        <v>3566</v>
+      </c>
+      <c r="AB30" s="0" t="s">
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>3678</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C31" s="0">
+        <v>3</v>
+      </c>
+      <c r="D31" s="0">
+        <v>2</v>
+      </c>
+      <c r="E31" s="0">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0">
+        <v>0</v>
+      </c>
+      <c r="G31" s="0">
+        <v>0</v>
+      </c>
+      <c r="H31" s="0">
+        <v>0</v>
+      </c>
+      <c r="I31" s="0">
+        <v>1</v>
+      </c>
+      <c r="J31" s="0">
+        <v>0</v>
+      </c>
+      <c r="K31" s="0">
+        <v>0</v>
+      </c>
+      <c r="L31" s="0">
+        <v>0</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0</v>
+      </c>
+      <c r="N31" s="0">
+        <v>0</v>
+      </c>
+      <c r="O31" s="0">
+        <v>0</v>
+      </c>
+      <c r="P31" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="0">
+        <v>1</v>
+      </c>
+      <c r="R31" s="0">
+        <v>3</v>
+      </c>
+      <c r="S31" s="0">
+        <v>7</v>
+      </c>
+      <c r="T31" s="0">
+        <v>66.7</v>
+      </c>
+      <c r="U31" s="0">
+        <v>913</v>
+      </c>
+      <c r="V31" s="0">
+        <v>3</v>
+      </c>
+      <c r="W31" s="0" t="s">
+        <v>3679</v>
+      </c>
+      <c r="X31" s="0" t="s">
+        <v>3680</v>
+      </c>
+      <c r="Y31" s="0" t="s">
+        <v>3681</v>
+      </c>
+      <c r="Z31" s="0" t="s">
+        <v>997</v>
+      </c>
+      <c r="AA31" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB31" s="0" t="s">
+        <v>3682</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>3683</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C32" s="0">
+        <v>3</v>
+      </c>
+      <c r="D32" s="0">
+        <v>0</v>
+      </c>
+      <c r="E32" s="0">
+        <v>0</v>
+      </c>
+      <c r="F32" s="0">
+        <v>0</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1</v>
+      </c>
+      <c r="H32" s="0">
+        <v>2</v>
+      </c>
+      <c r="I32" s="0">
+        <v>0</v>
+      </c>
+      <c r="J32" s="0">
+        <v>0</v>
+      </c>
+      <c r="K32" s="0">
+        <v>0</v>
+      </c>
+      <c r="L32" s="0">
+        <v>0</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0</v>
+      </c>
+      <c r="N32" s="0">
+        <v>0</v>
+      </c>
+      <c r="O32" s="0">
+        <v>0</v>
+      </c>
+      <c r="P32" s="0">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="0">
+        <v>1</v>
+      </c>
+      <c r="R32" s="0">
+        <v>7</v>
+      </c>
+      <c r="S32" s="0">
+        <v>8</v>
+      </c>
+      <c r="T32" s="0">
+        <v>0</v>
+      </c>
+      <c r="U32" s="0">
+        <v>900</v>
+      </c>
+      <c r="V32" s="0">
+        <v>2</v>
+      </c>
+      <c r="W32" s="0" t="s">
+        <v>3684</v>
+      </c>
+      <c r="X32" s="0" t="s">
+        <v>3685</v>
+      </c>
+      <c r="Y32" s="0" t="s">
+        <v>3686</v>
+      </c>
+      <c r="Z32" s="0" t="s">
+        <v>3687</v>
+      </c>
+      <c r="AA32" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB32" s="0" t="s">
+        <v>3688</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C33" s="0">
+        <v>3</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0">
+        <v>0</v>
+      </c>
+      <c r="F33" s="0">
+        <v>0</v>
+      </c>
+      <c r="G33" s="0">
+        <v>0</v>
+      </c>
+      <c r="H33" s="0">
+        <v>0</v>
+      </c>
+      <c r="I33" s="0">
+        <v>3</v>
+      </c>
+      <c r="J33" s="0">
+        <v>0</v>
+      </c>
+      <c r="K33" s="0">
+        <v>0</v>
+      </c>
+      <c r="L33" s="0">
+        <v>0</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0</v>
+      </c>
+      <c r="N33" s="0">
+        <v>0</v>
+      </c>
+      <c r="O33" s="0">
+        <v>0</v>
+      </c>
+      <c r="P33" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="0">
+        <v>1</v>
+      </c>
+      <c r="R33" s="0">
+        <v>4</v>
+      </c>
+      <c r="S33" s="0">
+        <v>4</v>
+      </c>
+      <c r="T33" s="0">
+        <v>33.3</v>
+      </c>
+      <c r="U33" s="0">
+        <v>978</v>
+      </c>
+      <c r="V33" s="0">
+        <v>3</v>
+      </c>
+      <c r="W33" s="0" t="s">
+        <v>3690</v>
+      </c>
+      <c r="X33" s="0" t="s">
+        <v>3677</v>
+      </c>
+      <c r="Y33" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z33" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="AA33" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB33" s="0" t="s">
+        <v>3689</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>3691</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C34" s="0">
+        <v>3</v>
+      </c>
+      <c r="D34" s="0">
+        <v>0</v>
+      </c>
+      <c r="E34" s="0">
+        <v>0</v>
+      </c>
+      <c r="F34" s="0">
+        <v>0</v>
+      </c>
+      <c r="G34" s="0">
+        <v>3</v>
+      </c>
+      <c r="H34" s="0">
+        <v>0</v>
+      </c>
+      <c r="I34" s="0">
+        <v>0</v>
+      </c>
+      <c r="J34" s="0">
+        <v>0</v>
+      </c>
+      <c r="K34" s="0">
+        <v>0</v>
+      </c>
+      <c r="L34" s="0">
+        <v>0</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0</v>
+      </c>
+      <c r="N34" s="0">
+        <v>0</v>
+      </c>
+      <c r="O34" s="0">
+        <v>0</v>
+      </c>
+      <c r="P34" s="0">
+        <v>4</v>
+      </c>
+      <c r="Q34" s="0">
+        <v>1</v>
+      </c>
+      <c r="R34" s="0">
+        <v>5</v>
+      </c>
+      <c r="S34" s="0">
+        <v>5</v>
+      </c>
+      <c r="T34" s="0">
+        <v>0</v>
+      </c>
+      <c r="U34" s="0">
+        <v>991</v>
+      </c>
+      <c r="V34" s="0">
+        <v>1</v>
+      </c>
+      <c r="W34" s="0" t="s">
+        <v>3692</v>
+      </c>
+      <c r="X34" s="0" t="s">
+        <v>3677</v>
+      </c>
+      <c r="Y34" s="0" t="s">
+        <v>3693</v>
+      </c>
+      <c r="Z34" s="0" t="s">
+        <v>3694</v>
+      </c>
+      <c r="AA34" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB34" s="0" t="s">
+        <v>3691</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>3695</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C35" s="0">
+        <v>1</v>
+      </c>
+      <c r="D35" s="0">
+        <v>0</v>
+      </c>
+      <c r="E35" s="0">
+        <v>0</v>
+      </c>
+      <c r="F35" s="0">
+        <v>0</v>
+      </c>
+      <c r="G35" s="0">
+        <v>1</v>
+      </c>
+      <c r="H35" s="0">
+        <v>0</v>
+      </c>
+      <c r="I35" s="0">
+        <v>0</v>
+      </c>
+      <c r="J35" s="0">
+        <v>0</v>
+      </c>
+      <c r="K35" s="0">
+        <v>0</v>
+      </c>
+      <c r="L35" s="0">
+        <v>0</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0</v>
+      </c>
+      <c r="N35" s="0">
+        <v>0</v>
+      </c>
+      <c r="O35" s="0">
+        <v>0</v>
+      </c>
+      <c r="P35" s="0">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="0">
+        <v>1</v>
+      </c>
+      <c r="R35" s="0">
+        <v>5</v>
+      </c>
+      <c r="S35" s="0">
+        <v>5</v>
+      </c>
+      <c r="T35" s="0">
+        <v>0</v>
+      </c>
+      <c r="U35" s="0">
+        <v>990</v>
+      </c>
+      <c r="V35" s="0">
+        <v>1</v>
+      </c>
+      <c r="W35" s="0" t="s">
+        <v>3696</v>
+      </c>
+      <c r="X35" s="0" t="s">
+        <v>3697</v>
+      </c>
+      <c r="Y35" s="0" t="s">
+        <v>3693</v>
+      </c>
+      <c r="Z35" s="0" t="s">
+        <v>3693</v>
+      </c>
+      <c r="AA35" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB35" s="0" t="s">
+        <v>3695</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>3698</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C36" s="0">
+        <v>1</v>
+      </c>
+      <c r="D36" s="0">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0">
+        <v>0</v>
+      </c>
+      <c r="F36" s="0">
+        <v>0</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1</v>
+      </c>
+      <c r="H36" s="0">
+        <v>0</v>
+      </c>
+      <c r="I36" s="0">
+        <v>0</v>
+      </c>
+      <c r="J36" s="0">
+        <v>0</v>
+      </c>
+      <c r="K36" s="0">
+        <v>0</v>
+      </c>
+      <c r="L36" s="0">
+        <v>0</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0</v>
+      </c>
+      <c r="N36" s="0">
+        <v>0</v>
+      </c>
+      <c r="O36" s="0">
+        <v>0</v>
+      </c>
+      <c r="P36" s="0">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="0">
+        <v>1</v>
+      </c>
+      <c r="R36" s="0">
+        <v>5</v>
+      </c>
+      <c r="S36" s="0">
+        <v>5</v>
+      </c>
+      <c r="T36" s="0">
+        <v>0</v>
+      </c>
+      <c r="U36" s="0">
+        <v>900</v>
+      </c>
+      <c r="V36" s="0">
+        <v>1</v>
+      </c>
+      <c r="W36" s="0" t="s">
+        <v>3699</v>
+      </c>
+      <c r="X36" s="0" t="s">
+        <v>3700</v>
+      </c>
+      <c r="Y36" s="0" t="s">
+        <v>3701</v>
+      </c>
+      <c r="Z36" s="0" t="s">
+        <v>3701</v>
+      </c>
+      <c r="AA36" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB36" s="0" t="s">
+        <v>3698</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>3702</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C37" s="0">
+        <v>1</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0">
+        <v>0</v>
+      </c>
+      <c r="H37" s="0">
+        <v>0</v>
+      </c>
+      <c r="I37" s="0">
+        <v>0</v>
+      </c>
+      <c r="J37" s="0">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0">
+        <v>0</v>
+      </c>
+      <c r="L37" s="0">
+        <v>0</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0</v>
+      </c>
+      <c r="N37" s="0">
+        <v>0</v>
+      </c>
+      <c r="O37" s="0">
+        <v>0</v>
+      </c>
+      <c r="P37" s="0">
+        <v>4</v>
+      </c>
+      <c r="Q37" s="0">
+        <v>1</v>
+      </c>
+      <c r="R37" s="0">
+        <v>5</v>
+      </c>
+      <c r="S37" s="0">
+        <v>5</v>
+      </c>
+      <c r="T37" s="0">
+        <v>0</v>
+      </c>
+      <c r="U37" s="0">
+        <v>919</v>
+      </c>
+      <c r="V37" s="0">
+        <v>1</v>
+      </c>
+      <c r="W37" s="0" t="s">
+        <v>3703</v>
+      </c>
+      <c r="X37" s="0" t="s">
+        <v>3700</v>
+      </c>
+      <c r="Y37" s="0" t="s">
+        <v>3704</v>
+      </c>
+      <c r="Z37" s="0" t="s">
+        <v>3704</v>
+      </c>
+      <c r="AA37" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB37" s="0" t="s">
+        <v>3702</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>3705</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C38" s="0">
+        <v>1</v>
+      </c>
+      <c r="D38" s="0">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0">
+        <v>1</v>
+      </c>
+      <c r="F38" s="0">
+        <v>0</v>
+      </c>
+      <c r="G38" s="0">
+        <v>0</v>
+      </c>
+      <c r="H38" s="0">
+        <v>0</v>
+      </c>
+      <c r="I38" s="0">
+        <v>0</v>
+      </c>
+      <c r="J38" s="0">
+        <v>0</v>
+      </c>
+      <c r="K38" s="0">
+        <v>0</v>
+      </c>
+      <c r="L38" s="0">
+        <v>0</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0</v>
+      </c>
+      <c r="N38" s="0">
+        <v>0</v>
+      </c>
+      <c r="O38" s="0">
+        <v>0</v>
+      </c>
+      <c r="P38" s="0">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="0">
+        <v>3</v>
+      </c>
+      <c r="R38" s="0">
+        <v>7</v>
+      </c>
+      <c r="S38" s="0">
+        <v>7</v>
+      </c>
+      <c r="T38" s="0">
+        <v>0</v>
+      </c>
+      <c r="U38" s="0">
+        <v>938</v>
+      </c>
+      <c r="V38" s="0">
+        <v>1</v>
+      </c>
+      <c r="W38" s="0" t="s">
+        <v>3706</v>
+      </c>
+      <c r="X38" s="0" t="s">
+        <v>3707</v>
+      </c>
+      <c r="Y38" s="0" t="s">
+        <v>3708</v>
+      </c>
+      <c r="Z38" s="0" t="s">
+        <v>3708</v>
+      </c>
+      <c r="AA38" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB38" s="0" t="s">
+        <v>3705</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>3709</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C39" s="0">
+        <v>1</v>
+      </c>
+      <c r="D39" s="0">
+        <v>0</v>
+      </c>
+      <c r="E39" s="0">
+        <v>0</v>
+      </c>
+      <c r="F39" s="0">
+        <v>0</v>
+      </c>
+      <c r="G39" s="0">
+        <v>0</v>
+      </c>
+      <c r="H39" s="0">
+        <v>0</v>
+      </c>
+      <c r="I39" s="0">
+        <v>1</v>
+      </c>
+      <c r="J39" s="0">
+        <v>0</v>
+      </c>
+      <c r="K39" s="0">
+        <v>0</v>
+      </c>
+      <c r="L39" s="0">
+        <v>0</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0</v>
+      </c>
+      <c r="N39" s="0">
+        <v>0</v>
+      </c>
+      <c r="O39" s="0">
+        <v>0</v>
+      </c>
+      <c r="P39" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="0">
+        <v>1</v>
+      </c>
+      <c r="R39" s="0">
+        <v>3</v>
+      </c>
+      <c r="S39" s="0">
+        <v>3</v>
+      </c>
+      <c r="T39" s="0">
+        <v>100</v>
+      </c>
+      <c r="U39" s="0">
+        <v>980</v>
+      </c>
+      <c r="V39" s="0">
+        <v>1</v>
+      </c>
+      <c r="W39" s="0" t="s">
+        <v>3710</v>
+      </c>
+      <c r="X39" s="0" t="s">
+        <v>3697</v>
+      </c>
+      <c r="Y39" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="Z39" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="AA39" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB39" s="0" t="s">
+        <v>3709</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>3711</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C40" s="0">
+        <v>1</v>
+      </c>
+      <c r="D40" s="0">
+        <v>0</v>
+      </c>
+      <c r="E40" s="0">
+        <v>1</v>
+      </c>
+      <c r="F40" s="0">
+        <v>0</v>
+      </c>
+      <c r="G40" s="0">
+        <v>0</v>
+      </c>
+      <c r="H40" s="0">
+        <v>0</v>
+      </c>
+      <c r="I40" s="0">
+        <v>0</v>
+      </c>
+      <c r="J40" s="0">
+        <v>0</v>
+      </c>
+      <c r="K40" s="0">
+        <v>0</v>
+      </c>
+      <c r="L40" s="0">
+        <v>0</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0</v>
+      </c>
+      <c r="N40" s="0">
+        <v>0</v>
+      </c>
+      <c r="O40" s="0">
+        <v>0</v>
+      </c>
+      <c r="P40" s="0">
+        <v>4</v>
+      </c>
+      <c r="Q40" s="0">
+        <v>1</v>
+      </c>
+      <c r="R40" s="0">
+        <v>5</v>
+      </c>
+      <c r="S40" s="0">
+        <v>5</v>
+      </c>
+      <c r="T40" s="0">
+        <v>0</v>
+      </c>
+      <c r="U40" s="0">
+        <v>990</v>
+      </c>
+      <c r="V40" s="0">
+        <v>1</v>
+      </c>
+      <c r="W40" s="0" t="s">
+        <v>3696</v>
+      </c>
+      <c r="X40" s="0" t="s">
+        <v>3697</v>
+      </c>
+      <c r="Y40" s="0" t="s">
+        <v>3712</v>
+      </c>
+      <c r="Z40" s="0" t="s">
+        <v>3712</v>
+      </c>
+      <c r="AA40" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB40" s="0" t="s">
+        <v>3711</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>3713</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C41" s="0">
+        <v>1</v>
+      </c>
+      <c r="D41" s="0">
+        <v>0</v>
+      </c>
+      <c r="E41" s="0">
+        <v>0</v>
+      </c>
+      <c r="F41" s="0">
+        <v>0</v>
+      </c>
+      <c r="G41" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" s="0">
+        <v>1</v>
+      </c>
+      <c r="I41" s="0">
+        <v>0</v>
+      </c>
+      <c r="J41" s="0">
+        <v>0</v>
+      </c>
+      <c r="K41" s="0">
+        <v>0</v>
+      </c>
+      <c r="L41" s="0">
+        <v>0</v>
+      </c>
+      <c r="M41" s="0">
+        <v>0</v>
+      </c>
+      <c r="N41" s="0">
+        <v>0</v>
+      </c>
+      <c r="O41" s="0">
+        <v>0</v>
+      </c>
+      <c r="P41" s="0">
+        <v>6</v>
+      </c>
+      <c r="Q41" s="0">
+        <v>3</v>
+      </c>
+      <c r="R41" s="0">
+        <v>9</v>
+      </c>
+      <c r="S41" s="0">
+        <v>9</v>
+      </c>
+      <c r="T41" s="0">
+        <v>0</v>
+      </c>
+      <c r="U41" s="0">
+        <v>900</v>
+      </c>
+      <c r="V41" s="0">
+        <v>1</v>
+      </c>
+      <c r="W41" s="0" t="s">
+        <v>3714</v>
+      </c>
+      <c r="X41" s="0" t="s">
+        <v>3700</v>
+      </c>
+      <c r="Y41" s="0" t="s">
+        <v>3715</v>
+      </c>
+      <c r="Z41" s="0" t="s">
+        <v>3715</v>
+      </c>
+      <c r="AA41" s="0" t="s">
+        <v>3591</v>
+      </c>
+      <c r="AB41" s="0" t="s">
+        <v>3713</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AB41"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:R40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.0636444091797" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.99956464767456" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.71822118759155" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.1756238937378" customWidth="1"/>
+    <col min="12" max="12" width="16.9451551437378" customWidth="1"/>
+    <col min="13" max="13" width="10.0190024375916" customWidth="1"/>
+    <col min="14" max="14" width="26.4770545959473" customWidth="1"/>
+    <col min="15" max="15" width="11.667160987854" customWidth="1"/>
+    <col min="16" max="16" width="34.6001930236816" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" customWidth="1"/>
+    <col min="18" max="18" width="37.6097717285156" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="s">
+        <v>3716</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>3717</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>3718</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>3574</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>3596</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>3568</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>3581</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>3592</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>3561</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>3604</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>3609</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>3600</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>3625</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>3629</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>3636</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>3719</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>3720</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>3721</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C2" s="0">
+        <v>229</v>
+      </c>
+      <c r="D2" s="0">
+        <v>88</v>
+      </c>
+      <c r="E2" s="0">
+        <v>33</v>
+      </c>
+      <c r="F2" s="0">
+        <v>30</v>
+      </c>
+      <c r="G2" s="0">
+        <v>33</v>
+      </c>
+      <c r="H2" s="0">
+        <v>15</v>
+      </c>
+      <c r="I2" s="0">
+        <v>27</v>
+      </c>
+      <c r="J2" s="0">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0">
+        <v>0</v>
+      </c>
+      <c r="L2" s="0">
+        <v>0</v>
+      </c>
+      <c r="M2" s="0">
+        <v>0</v>
+      </c>
+      <c r="N2" s="0">
+        <v>0</v>
+      </c>
+      <c r="O2" s="0">
+        <v>0</v>
+      </c>
+      <c r="P2" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="0">
+        <v>2</v>
+      </c>
+      <c r="R2" s="0" t="s">
+        <v>3722</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>3723</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C3" s="0">
+        <v>189</v>
+      </c>
+      <c r="D3" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3" s="0">
+        <v>23</v>
+      </c>
+      <c r="F3" s="0">
+        <v>35</v>
+      </c>
+      <c r="G3" s="0">
+        <v>9</v>
+      </c>
+      <c r="H3" s="0">
+        <v>10</v>
+      </c>
+      <c r="I3" s="0">
+        <v>8</v>
+      </c>
+      <c r="J3" s="0">
+        <v>70</v>
+      </c>
+      <c r="K3" s="0">
+        <v>2</v>
+      </c>
+      <c r="L3" s="0">
+        <v>0</v>
+      </c>
+      <c r="M3" s="0">
+        <v>0</v>
+      </c>
+      <c r="N3" s="0">
+        <v>0</v>
+      </c>
+      <c r="O3" s="0">
+        <v>0</v>
+      </c>
+      <c r="P3" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="0">
+        <v>2</v>
+      </c>
+      <c r="R3" s="0" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>3725</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C4" s="0">
+        <v>166</v>
+      </c>
+      <c r="D4" s="0">
+        <v>136</v>
+      </c>
+      <c r="E4" s="0">
+        <v>2</v>
+      </c>
+      <c r="F4" s="0">
+        <v>7</v>
+      </c>
+      <c r="G4" s="0">
+        <v>5</v>
+      </c>
+      <c r="H4" s="0">
+        <v>5</v>
+      </c>
+      <c r="I4" s="0">
+        <v>9</v>
+      </c>
+      <c r="J4" s="0">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0">
+        <v>0</v>
+      </c>
+      <c r="L4" s="0">
+        <v>0</v>
+      </c>
+      <c r="M4" s="0">
+        <v>0</v>
+      </c>
+      <c r="N4" s="0">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0">
+        <v>0</v>
+      </c>
+      <c r="P4" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="0">
+        <v>2</v>
+      </c>
+      <c r="R4" s="0" t="s">
+        <v>3726</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C5" s="0">
+        <v>146</v>
+      </c>
+      <c r="D5" s="0">
+        <v>113</v>
+      </c>
+      <c r="E5" s="0">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0">
+        <v>8</v>
+      </c>
+      <c r="G5" s="0">
+        <v>10</v>
+      </c>
+      <c r="H5" s="0">
+        <v>12</v>
+      </c>
+      <c r="I5" s="0">
+        <v>2</v>
+      </c>
+      <c r="J5" s="0">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0">
+        <v>0</v>
+      </c>
+      <c r="N5" s="0">
+        <v>0</v>
+      </c>
+      <c r="O5" s="0">
+        <v>0</v>
+      </c>
+      <c r="P5" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="0">
+        <v>1</v>
+      </c>
+      <c r="R5" s="0" t="s">
+        <v>3728</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>3729</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C6" s="0">
+        <v>124</v>
+      </c>
+      <c r="D6" s="0">
+        <v>65</v>
+      </c>
+      <c r="E6" s="0">
+        <v>11</v>
+      </c>
+      <c r="F6" s="0">
+        <v>16</v>
+      </c>
+      <c r="G6" s="0">
+        <v>3</v>
+      </c>
+      <c r="H6" s="0">
+        <v>7</v>
+      </c>
+      <c r="I6" s="0">
+        <v>22</v>
+      </c>
+      <c r="J6" s="0">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0">
+        <v>0</v>
+      </c>
+      <c r="L6" s="0">
+        <v>0</v>
+      </c>
+      <c r="M6" s="0">
+        <v>0</v>
+      </c>
+      <c r="N6" s="0">
+        <v>0</v>
+      </c>
+      <c r="O6" s="0">
+        <v>0</v>
+      </c>
+      <c r="P6" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="0">
+        <v>0</v>
+      </c>
+      <c r="R6" s="0" t="s">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>3731</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C7" s="0">
+        <v>109</v>
+      </c>
+      <c r="D7" s="0">
+        <v>61</v>
+      </c>
+      <c r="E7" s="0">
+        <v>3</v>
+      </c>
+      <c r="F7" s="0">
+        <v>17</v>
+      </c>
+      <c r="G7" s="0">
+        <v>18</v>
+      </c>
+      <c r="H7" s="0">
+        <v>4</v>
+      </c>
+      <c r="I7" s="0">
+        <v>6</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0">
+        <v>0</v>
+      </c>
+      <c r="N7" s="0">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0">
+        <v>0</v>
+      </c>
+      <c r="P7" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="0">
+        <v>0</v>
+      </c>
+      <c r="R7" s="0" t="s">
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>3733</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C8" s="0">
+        <v>93</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0</v>
+      </c>
+      <c r="H8" s="0">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0">
+        <v>25</v>
+      </c>
+      <c r="L8" s="0">
+        <v>58</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0">
+        <v>3</v>
+      </c>
+      <c r="O8" s="0">
+        <v>0</v>
+      </c>
+      <c r="P8" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>7</v>
+      </c>
+      <c r="R8" s="0" t="s">
+        <v>3734</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>3735</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C9" s="0">
+        <v>43</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0">
+        <v>1</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0">
+        <v>11</v>
+      </c>
+      <c r="L9" s="0">
+        <v>2</v>
+      </c>
+      <c r="M9" s="0">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0">
+        <v>18</v>
+      </c>
+      <c r="O9" s="0">
+        <v>0</v>
+      </c>
+      <c r="P9" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="0">
+        <v>11</v>
+      </c>
+      <c r="R9" s="0" t="s">
+        <v>3736</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>3737</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C10" s="0">
+        <v>41</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0</v>
+      </c>
+      <c r="H10" s="0">
+        <v>23</v>
+      </c>
+      <c r="I10" s="0">
+        <v>2</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0">
+        <v>0</v>
+      </c>
+      <c r="M10" s="0">
+        <v>16</v>
+      </c>
+      <c r="N10" s="0">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0">
+        <v>0</v>
+      </c>
+      <c r="P10" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="0">
+        <v>0</v>
+      </c>
+      <c r="R10" s="0" t="s">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>3739</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C11" s="0">
+        <v>37</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" s="0">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0">
+        <v>13</v>
+      </c>
+      <c r="L11" s="0">
+        <v>0</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0">
+        <v>21</v>
+      </c>
+      <c r="P11" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="0">
+        <v>3</v>
+      </c>
+      <c r="R11" s="0" t="s">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>3741</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C12" s="0">
+        <v>35</v>
+      </c>
+      <c r="D12" s="0">
+        <v>16</v>
+      </c>
+      <c r="E12" s="0">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0">
+        <v>8</v>
+      </c>
+      <c r="G12" s="0">
+        <v>6</v>
+      </c>
+      <c r="H12" s="0">
+        <v>2</v>
+      </c>
+      <c r="I12" s="0">
+        <v>3</v>
+      </c>
+      <c r="J12" s="0">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0">
+        <v>0</v>
+      </c>
+      <c r="L12" s="0">
+        <v>0</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0">
+        <v>0</v>
+      </c>
+      <c r="P12" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="0">
+        <v>0</v>
+      </c>
+      <c r="R12" s="0" t="s">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>3743</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C13" s="0">
+        <v>26</v>
+      </c>
+      <c r="D13" s="0">
+        <v>16</v>
+      </c>
+      <c r="E13" s="0">
+        <v>1</v>
+      </c>
+      <c r="F13" s="0">
+        <v>2</v>
+      </c>
+      <c r="G13" s="0">
+        <v>3</v>
+      </c>
+      <c r="H13" s="0">
+        <v>1</v>
+      </c>
+      <c r="I13" s="0">
+        <v>3</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0">
+        <v>0</v>
+      </c>
+      <c r="L13" s="0">
+        <v>0</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0">
+        <v>0</v>
+      </c>
+      <c r="O13" s="0">
+        <v>0</v>
+      </c>
+      <c r="P13" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="0">
+        <v>0</v>
+      </c>
+      <c r="R13" s="0" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>3745</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C14" s="0">
+        <v>25</v>
+      </c>
+      <c r="D14" s="0">
+        <v>9</v>
+      </c>
+      <c r="E14" s="0">
+        <v>10</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>6</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0">
+        <v>0</v>
+      </c>
+      <c r="P14" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>0</v>
+      </c>
+      <c r="R14" s="0" t="s">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>3747</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C15" s="0">
+        <v>24</v>
+      </c>
+      <c r="D15" s="0">
+        <v>15</v>
+      </c>
+      <c r="E15" s="0">
+        <v>3</v>
+      </c>
+      <c r="F15" s="0">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0">
+        <v>3</v>
+      </c>
+      <c r="H15" s="0">
+        <v>0</v>
+      </c>
+      <c r="I15" s="0">
+        <v>1</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0">
+        <v>0</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0</v>
+      </c>
+      <c r="N15" s="0">
+        <v>0</v>
+      </c>
+      <c r="O15" s="0">
+        <v>0</v>
+      </c>
+      <c r="P15" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="0">
+        <v>1</v>
+      </c>
+      <c r="R15" s="0" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>3748</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C16" s="0">
+        <v>21</v>
+      </c>
+      <c r="D16" s="0">
+        <v>9</v>
+      </c>
+      <c r="E16" s="0">
+        <v>10</v>
+      </c>
+      <c r="F16" s="0">
+        <v>0</v>
+      </c>
+      <c r="G16" s="0">
+        <v>2</v>
+      </c>
+      <c r="H16" s="0">
+        <v>0</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0">
+        <v>0</v>
+      </c>
+      <c r="L16" s="0">
+        <v>0</v>
+      </c>
+      <c r="M16" s="0">
+        <v>0</v>
+      </c>
+      <c r="N16" s="0">
+        <v>0</v>
+      </c>
+      <c r="O16" s="0">
+        <v>0</v>
+      </c>
+      <c r="P16" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="0">
+        <v>0</v>
+      </c>
+      <c r="R16" s="0" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>3750</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C17" s="0">
+        <v>21</v>
+      </c>
+      <c r="D17" s="0">
+        <v>4</v>
+      </c>
+      <c r="E17" s="0">
+        <v>12</v>
+      </c>
+      <c r="F17" s="0">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0">
+        <v>5</v>
+      </c>
+      <c r="H17" s="0">
+        <v>0</v>
+      </c>
+      <c r="I17" s="0">
+        <v>0</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0">
+        <v>0</v>
+      </c>
+      <c r="L17" s="0">
+        <v>0</v>
+      </c>
+      <c r="M17" s="0">
+        <v>0</v>
+      </c>
+      <c r="N17" s="0">
+        <v>0</v>
+      </c>
+      <c r="O17" s="0">
+        <v>0</v>
+      </c>
+      <c r="P17" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="0">
+        <v>0</v>
+      </c>
+      <c r="R17" s="0" t="s">
+        <v>3751</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>3752</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C18" s="0">
+        <v>17</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0">
+        <v>0</v>
+      </c>
+      <c r="H18" s="0">
+        <v>0</v>
+      </c>
+      <c r="I18" s="0">
+        <v>0</v>
+      </c>
+      <c r="J18" s="0">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0">
+        <v>7</v>
+      </c>
+      <c r="L18" s="0">
+        <v>0</v>
+      </c>
+      <c r="M18" s="0">
+        <v>0</v>
+      </c>
+      <c r="N18" s="0">
+        <v>0</v>
+      </c>
+      <c r="O18" s="0">
+        <v>0</v>
+      </c>
+      <c r="P18" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="0">
+        <v>10</v>
+      </c>
+      <c r="R18" s="0" t="s">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>3754</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C19" s="0">
+        <v>15</v>
+      </c>
+      <c r="D19" s="0">
+        <v>4</v>
+      </c>
+      <c r="E19" s="0">
+        <v>8</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0">
+        <v>3</v>
+      </c>
+      <c r="H19" s="0">
+        <v>0</v>
+      </c>
+      <c r="I19" s="0">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0">
+        <v>0</v>
+      </c>
+      <c r="M19" s="0">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0">
+        <v>0</v>
+      </c>
+      <c r="O19" s="0">
+        <v>0</v>
+      </c>
+      <c r="P19" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="0">
+        <v>0</v>
+      </c>
+      <c r="R19" s="0" t="s">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>3756</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C20" s="0">
+        <v>14</v>
+      </c>
+      <c r="D20" s="0">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0">
+        <v>0</v>
+      </c>
+      <c r="H20" s="0">
+        <v>0</v>
+      </c>
+      <c r="I20" s="0">
+        <v>0</v>
+      </c>
+      <c r="J20" s="0">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0">
+        <v>2</v>
+      </c>
+      <c r="L20" s="0">
+        <v>0</v>
+      </c>
+      <c r="M20" s="0">
+        <v>0</v>
+      </c>
+      <c r="N20" s="0">
+        <v>0</v>
+      </c>
+      <c r="O20" s="0">
+        <v>0</v>
+      </c>
+      <c r="P20" s="0">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="0">
+        <v>0</v>
+      </c>
+      <c r="R20" s="0" t="s">
+        <v>3757</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>3758</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C21" s="0">
+        <v>14</v>
+      </c>
+      <c r="D21" s="0">
+        <v>10</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0</v>
+      </c>
+      <c r="F21" s="0">
+        <v>0</v>
+      </c>
+      <c r="G21" s="0">
+        <v>2</v>
+      </c>
+      <c r="H21" s="0">
+        <v>1</v>
+      </c>
+      <c r="I21" s="0">
+        <v>1</v>
+      </c>
+      <c r="J21" s="0">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0">
+        <v>0</v>
+      </c>
+      <c r="L21" s="0">
+        <v>0</v>
+      </c>
+      <c r="M21" s="0">
+        <v>0</v>
+      </c>
+      <c r="N21" s="0">
+        <v>0</v>
+      </c>
+      <c r="O21" s="0">
+        <v>0</v>
+      </c>
+      <c r="P21" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="0">
+        <v>0</v>
+      </c>
+      <c r="R21" s="0" t="s">
+        <v>3759</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>3760</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C22" s="0">
+        <v>11</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0</v>
+      </c>
+      <c r="E22" s="0">
+        <v>8</v>
+      </c>
+      <c r="F22" s="0">
+        <v>0</v>
+      </c>
+      <c r="G22" s="0">
+        <v>3</v>
+      </c>
+      <c r="H22" s="0">
+        <v>0</v>
+      </c>
+      <c r="I22" s="0">
+        <v>0</v>
+      </c>
+      <c r="J22" s="0">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0">
+        <v>0</v>
+      </c>
+      <c r="L22" s="0">
+        <v>0</v>
+      </c>
+      <c r="M22" s="0">
+        <v>0</v>
+      </c>
+      <c r="N22" s="0">
+        <v>0</v>
+      </c>
+      <c r="O22" s="0">
+        <v>0</v>
+      </c>
+      <c r="P22" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="0">
+        <v>0</v>
+      </c>
+      <c r="R22" s="0" t="s">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>3762</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C23" s="0">
+        <v>10</v>
+      </c>
+      <c r="D23" s="0">
+        <v>4</v>
+      </c>
+      <c r="E23" s="0">
+        <v>4</v>
+      </c>
+      <c r="F23" s="0">
+        <v>0</v>
+      </c>
+      <c r="G23" s="0">
+        <v>2</v>
+      </c>
+      <c r="H23" s="0">
+        <v>0</v>
+      </c>
+      <c r="I23" s="0">
+        <v>0</v>
+      </c>
+      <c r="J23" s="0">
+        <v>0</v>
+      </c>
+      <c r="K23" s="0">
+        <v>0</v>
+      </c>
+      <c r="L23" s="0">
+        <v>0</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0</v>
+      </c>
+      <c r="N23" s="0">
+        <v>0</v>
+      </c>
+      <c r="O23" s="0">
+        <v>0</v>
+      </c>
+      <c r="P23" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="0">
+        <v>0</v>
+      </c>
+      <c r="R23" s="0" t="s">
+        <v>3763</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>3764</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C24" s="0">
+        <v>10</v>
+      </c>
+      <c r="D24" s="0">
+        <v>1</v>
+      </c>
+      <c r="E24" s="0">
+        <v>8</v>
+      </c>
+      <c r="F24" s="0">
+        <v>0</v>
+      </c>
+      <c r="G24" s="0">
+        <v>1</v>
+      </c>
+      <c r="H24" s="0">
+        <v>0</v>
+      </c>
+      <c r="I24" s="0">
+        <v>0</v>
+      </c>
+      <c r="J24" s="0">
+        <v>0</v>
+      </c>
+      <c r="K24" s="0">
+        <v>0</v>
+      </c>
+      <c r="L24" s="0">
+        <v>0</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0</v>
+      </c>
+      <c r="N24" s="0">
+        <v>0</v>
+      </c>
+      <c r="O24" s="0">
+        <v>0</v>
+      </c>
+      <c r="P24" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="0">
+        <v>0</v>
+      </c>
+      <c r="R24" s="0" t="s">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>3766</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C25" s="0">
+        <v>10</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0">
+        <v>0</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0</v>
+      </c>
+      <c r="I25" s="0">
+        <v>0</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0</v>
+      </c>
+      <c r="K25" s="0">
+        <v>10</v>
+      </c>
+      <c r="L25" s="0">
+        <v>0</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0</v>
+      </c>
+      <c r="N25" s="0">
+        <v>0</v>
+      </c>
+      <c r="O25" s="0">
+        <v>0</v>
+      </c>
+      <c r="P25" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="0">
+        <v>0</v>
+      </c>
+      <c r="R25" s="0" t="s">
+        <v>3767</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>3768</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C26" s="0">
+        <v>9</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0">
+        <v>0</v>
+      </c>
+      <c r="G26" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0">
+        <v>0</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0</v>
+      </c>
+      <c r="K26" s="0">
+        <v>0</v>
+      </c>
+      <c r="L26" s="0">
+        <v>0</v>
+      </c>
+      <c r="M26" s="0">
+        <v>9</v>
+      </c>
+      <c r="N26" s="0">
+        <v>0</v>
+      </c>
+      <c r="O26" s="0">
+        <v>0</v>
+      </c>
+      <c r="P26" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="0">
+        <v>0</v>
+      </c>
+      <c r="R26" s="0" t="s">
+        <v>3769</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>3770</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C27" s="0">
+        <v>8</v>
+      </c>
+      <c r="D27" s="0">
+        <v>7</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0">
+        <v>0</v>
+      </c>
+      <c r="G27" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" s="0">
+        <v>1</v>
+      </c>
+      <c r="I27" s="0">
+        <v>0</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0</v>
+      </c>
+      <c r="K27" s="0">
+        <v>0</v>
+      </c>
+      <c r="L27" s="0">
+        <v>0</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0</v>
+      </c>
+      <c r="N27" s="0">
+        <v>0</v>
+      </c>
+      <c r="O27" s="0">
+        <v>0</v>
+      </c>
+      <c r="P27" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>0</v>
+      </c>
+      <c r="R27" s="0" t="s">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>3772</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C28" s="0">
+        <v>6</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0</v>
+      </c>
+      <c r="F28" s="0">
+        <v>0</v>
+      </c>
+      <c r="G28" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" s="0">
+        <v>5</v>
+      </c>
+      <c r="I28" s="0">
+        <v>0</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0</v>
+      </c>
+      <c r="K28" s="0">
+        <v>0</v>
+      </c>
+      <c r="L28" s="0">
+        <v>0</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0</v>
+      </c>
+      <c r="N28" s="0">
+        <v>0</v>
+      </c>
+      <c r="O28" s="0">
+        <v>0</v>
+      </c>
+      <c r="P28" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>0</v>
+      </c>
+      <c r="R28" s="0" t="s">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C29" s="0">
+        <v>5</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1</v>
+      </c>
+      <c r="E29" s="0">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0">
+        <v>2</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1</v>
+      </c>
+      <c r="H29" s="0">
+        <v>1</v>
+      </c>
+      <c r="I29" s="0">
+        <v>0</v>
+      </c>
+      <c r="J29" s="0">
+        <v>0</v>
+      </c>
+      <c r="K29" s="0">
+        <v>0</v>
+      </c>
+      <c r="L29" s="0">
+        <v>0</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0</v>
+      </c>
+      <c r="N29" s="0">
+        <v>0</v>
+      </c>
+      <c r="O29" s="0">
+        <v>0</v>
+      </c>
+      <c r="P29" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="0">
+        <v>0</v>
+      </c>
+      <c r="R29" s="0" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>3776</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C30" s="0">
+        <v>4</v>
+      </c>
+      <c r="D30" s="0">
+        <v>0</v>
+      </c>
+      <c r="E30" s="0">
+        <v>4</v>
+      </c>
+      <c r="F30" s="0">
+        <v>0</v>
+      </c>
+      <c r="G30" s="0">
+        <v>0</v>
+      </c>
+      <c r="H30" s="0">
+        <v>0</v>
+      </c>
+      <c r="I30" s="0">
+        <v>0</v>
+      </c>
+      <c r="J30" s="0">
+        <v>0</v>
+      </c>
+      <c r="K30" s="0">
+        <v>0</v>
+      </c>
+      <c r="L30" s="0">
+        <v>0</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0</v>
+      </c>
+      <c r="N30" s="0">
+        <v>0</v>
+      </c>
+      <c r="O30" s="0">
+        <v>0</v>
+      </c>
+      <c r="P30" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="0">
+        <v>0</v>
+      </c>
+      <c r="R30" s="0" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>3778</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C31" s="0">
+        <v>4</v>
+      </c>
+      <c r="D31" s="0">
+        <v>0</v>
+      </c>
+      <c r="E31" s="0">
+        <v>1</v>
+      </c>
+      <c r="F31" s="0">
+        <v>0</v>
+      </c>
+      <c r="G31" s="0">
+        <v>3</v>
+      </c>
+      <c r="H31" s="0">
+        <v>0</v>
+      </c>
+      <c r="I31" s="0">
+        <v>0</v>
+      </c>
+      <c r="J31" s="0">
+        <v>0</v>
+      </c>
+      <c r="K31" s="0">
+        <v>0</v>
+      </c>
+      <c r="L31" s="0">
+        <v>0</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0</v>
+      </c>
+      <c r="N31" s="0">
+        <v>0</v>
+      </c>
+      <c r="O31" s="0">
+        <v>0</v>
+      </c>
+      <c r="P31" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="0">
+        <v>0</v>
+      </c>
+      <c r="R31" s="0" t="s">
+        <v>3779</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>3780</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C32" s="0">
+        <v>2</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1</v>
+      </c>
+      <c r="E32" s="0">
+        <v>1</v>
+      </c>
+      <c r="F32" s="0">
+        <v>0</v>
+      </c>
+      <c r="G32" s="0">
+        <v>0</v>
+      </c>
+      <c r="H32" s="0">
+        <v>0</v>
+      </c>
+      <c r="I32" s="0">
+        <v>0</v>
+      </c>
+      <c r="J32" s="0">
+        <v>0</v>
+      </c>
+      <c r="K32" s="0">
+        <v>0</v>
+      </c>
+      <c r="L32" s="0">
+        <v>0</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0</v>
+      </c>
+      <c r="N32" s="0">
+        <v>0</v>
+      </c>
+      <c r="O32" s="0">
+        <v>0</v>
+      </c>
+      <c r="P32" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="0">
+        <v>0</v>
+      </c>
+      <c r="R32" s="0" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>3782</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C33" s="0">
+        <v>2</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1</v>
+      </c>
+      <c r="E33" s="0">
+        <v>1</v>
+      </c>
+      <c r="F33" s="0">
+        <v>0</v>
+      </c>
+      <c r="G33" s="0">
+        <v>0</v>
+      </c>
+      <c r="H33" s="0">
+        <v>0</v>
+      </c>
+      <c r="I33" s="0">
+        <v>0</v>
+      </c>
+      <c r="J33" s="0">
+        <v>0</v>
+      </c>
+      <c r="K33" s="0">
+        <v>0</v>
+      </c>
+      <c r="L33" s="0">
+        <v>0</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0</v>
+      </c>
+      <c r="N33" s="0">
+        <v>0</v>
+      </c>
+      <c r="O33" s="0">
+        <v>0</v>
+      </c>
+      <c r="P33" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="0">
+        <v>0</v>
+      </c>
+      <c r="R33" s="0" t="s">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>3784</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C34" s="0">
+        <v>1</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1</v>
+      </c>
+      <c r="E34" s="0">
+        <v>0</v>
+      </c>
+      <c r="F34" s="0">
+        <v>0</v>
+      </c>
+      <c r="G34" s="0">
+        <v>0</v>
+      </c>
+      <c r="H34" s="0">
+        <v>0</v>
+      </c>
+      <c r="I34" s="0">
+        <v>0</v>
+      </c>
+      <c r="J34" s="0">
+        <v>0</v>
+      </c>
+      <c r="K34" s="0">
+        <v>0</v>
+      </c>
+      <c r="L34" s="0">
+        <v>0</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0</v>
+      </c>
+      <c r="N34" s="0">
+        <v>0</v>
+      </c>
+      <c r="O34" s="0">
+        <v>0</v>
+      </c>
+      <c r="P34" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="0">
+        <v>0</v>
+      </c>
+      <c r="R34" s="0" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>3786</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C35" s="0">
+        <v>1</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1</v>
+      </c>
+      <c r="E35" s="0">
+        <v>0</v>
+      </c>
+      <c r="F35" s="0">
+        <v>0</v>
+      </c>
+      <c r="G35" s="0">
+        <v>0</v>
+      </c>
+      <c r="H35" s="0">
+        <v>0</v>
+      </c>
+      <c r="I35" s="0">
+        <v>0</v>
+      </c>
+      <c r="J35" s="0">
+        <v>0</v>
+      </c>
+      <c r="K35" s="0">
+        <v>0</v>
+      </c>
+      <c r="L35" s="0">
+        <v>0</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0</v>
+      </c>
+      <c r="N35" s="0">
+        <v>0</v>
+      </c>
+      <c r="O35" s="0">
+        <v>0</v>
+      </c>
+      <c r="P35" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="0">
+        <v>0</v>
+      </c>
+      <c r="R35" s="0" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>3787</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C36" s="0">
+        <v>1</v>
+      </c>
+      <c r="D36" s="0">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0">
+        <v>1</v>
+      </c>
+      <c r="F36" s="0">
+        <v>0</v>
+      </c>
+      <c r="G36" s="0">
+        <v>0</v>
+      </c>
+      <c r="H36" s="0">
+        <v>0</v>
+      </c>
+      <c r="I36" s="0">
+        <v>0</v>
+      </c>
+      <c r="J36" s="0">
+        <v>0</v>
+      </c>
+      <c r="K36" s="0">
+        <v>0</v>
+      </c>
+      <c r="L36" s="0">
+        <v>0</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0</v>
+      </c>
+      <c r="N36" s="0">
+        <v>0</v>
+      </c>
+      <c r="O36" s="0">
+        <v>0</v>
+      </c>
+      <c r="P36" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="0">
+        <v>0</v>
+      </c>
+      <c r="R36" s="0" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>3788</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C37" s="0">
+        <v>1</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0">
+        <v>0</v>
+      </c>
+      <c r="H37" s="0">
+        <v>0</v>
+      </c>
+      <c r="I37" s="0">
+        <v>0</v>
+      </c>
+      <c r="J37" s="0">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0">
+        <v>0</v>
+      </c>
+      <c r="L37" s="0">
+        <v>0</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0</v>
+      </c>
+      <c r="N37" s="0">
+        <v>0</v>
+      </c>
+      <c r="O37" s="0">
+        <v>0</v>
+      </c>
+      <c r="P37" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="0">
+        <v>0</v>
+      </c>
+      <c r="R37" s="0" t="s">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>3790</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C38" s="0">
+        <v>1</v>
+      </c>
+      <c r="D38" s="0">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0">
+        <v>1</v>
+      </c>
+      <c r="F38" s="0">
+        <v>0</v>
+      </c>
+      <c r="G38" s="0">
+        <v>0</v>
+      </c>
+      <c r="H38" s="0">
+        <v>0</v>
+      </c>
+      <c r="I38" s="0">
+        <v>0</v>
+      </c>
+      <c r="J38" s="0">
+        <v>0</v>
+      </c>
+      <c r="K38" s="0">
+        <v>0</v>
+      </c>
+      <c r="L38" s="0">
+        <v>0</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0</v>
+      </c>
+      <c r="N38" s="0">
+        <v>0</v>
+      </c>
+      <c r="O38" s="0">
+        <v>0</v>
+      </c>
+      <c r="P38" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="0">
+        <v>0</v>
+      </c>
+      <c r="R38" s="0" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>3791</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C39" s="0">
+        <v>1</v>
+      </c>
+      <c r="D39" s="0">
+        <v>0</v>
+      </c>
+      <c r="E39" s="0">
+        <v>1</v>
+      </c>
+      <c r="F39" s="0">
+        <v>0</v>
+      </c>
+      <c r="G39" s="0">
+        <v>0</v>
+      </c>
+      <c r="H39" s="0">
+        <v>0</v>
+      </c>
+      <c r="I39" s="0">
+        <v>0</v>
+      </c>
+      <c r="J39" s="0">
+        <v>0</v>
+      </c>
+      <c r="K39" s="0">
+        <v>0</v>
+      </c>
+      <c r="L39" s="0">
+        <v>0</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0</v>
+      </c>
+      <c r="N39" s="0">
+        <v>0</v>
+      </c>
+      <c r="O39" s="0">
+        <v>0</v>
+      </c>
+      <c r="P39" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="0">
+        <v>0</v>
+      </c>
+      <c r="R39" s="0" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="C40" s="0">
+        <v>1476</v>
+      </c>
+      <c r="D40" s="0">
+        <v>594</v>
+      </c>
+      <c r="E40" s="0">
+        <v>146</v>
+      </c>
+      <c r="F40" s="0">
+        <v>127</v>
+      </c>
+      <c r="G40" s="0">
+        <v>118</v>
+      </c>
+      <c r="H40" s="0">
+        <v>87</v>
+      </c>
+      <c r="I40" s="0">
+        <v>85</v>
+      </c>
+      <c r="J40" s="0">
+        <v>71</v>
+      </c>
+      <c r="K40" s="0">
+        <v>70</v>
+      </c>
+      <c r="L40" s="0">
+        <v>60</v>
+      </c>
+      <c r="M40" s="0">
+        <v>25</v>
+      </c>
+      <c r="N40" s="0">
+        <v>21</v>
+      </c>
+      <c r="O40" s="0">
+        <v>21</v>
+      </c>
+      <c r="P40" s="0">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="0">
+        <v>39</v>
+      </c>
+      <c r="R40" s="0" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R40"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.182785987854" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="25.8345680236816" customWidth="1"/>
+    <col min="6" max="6" width="19.8394069671631" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.8305721282959" customWidth="1"/>
+    <col min="9" max="9" width="11.1198215484619" customWidth="1"/>
+    <col min="10" max="10" width="10.4831943511963" customWidth="1"/>
+    <col min="11" max="11" width="17.3684253692627" customWidth="1"/>
+    <col min="12" max="12" width="11.1198215484619" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="13.5536937713623" customWidth="1"/>
+    <col min="15" max="15" width="17.422926902771" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="s">
+        <v>3793</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>3794</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>3569</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3586</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3795</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>3796</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>3797</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>3798</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>3799</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>3800</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>3801</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>3802</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>3803</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>3546</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>2019</v>
+      </c>
+      <c r="B2" s="0">
+        <v>449</v>
+      </c>
+      <c r="C2" s="0">
+        <v>449</v>
+      </c>
+      <c r="D2" s="0">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0">
+        <v>3</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>3568</v>
+      </c>
+      <c r="H2" s="0">
+        <v>233</v>
+      </c>
+      <c r="I2" s="0">
+        <v>52.2</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>3804</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>3805</v>
+      </c>
+      <c r="L2" s="0">
+        <v>93.5</v>
+      </c>
+      <c r="M2" s="0">
+        <v>3991</v>
+      </c>
+      <c r="N2" s="0">
+        <v>22</v>
+      </c>
+      <c r="O2" s="0">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="0">
+        <v>588</v>
+      </c>
+      <c r="C3" s="0">
+        <v>546</v>
+      </c>
+      <c r="D3" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3" s="0">
+        <v>11</v>
+      </c>
+      <c r="F3" s="0">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>3561</v>
+      </c>
+      <c r="H3" s="0">
+        <v>301</v>
+      </c>
+      <c r="I3" s="0">
+        <v>51.2</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>3806</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>3807</v>
+      </c>
+      <c r="L3" s="0">
+        <v>92.9</v>
+      </c>
+      <c r="M3" s="0">
+        <v>4002</v>
+      </c>
+      <c r="N3" s="0">
+        <v>23</v>
+      </c>
+      <c r="O3" s="0">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="0">
+        <v>813</v>
+      </c>
+      <c r="C4" s="0">
+        <v>766</v>
+      </c>
+      <c r="D4" s="0">
+        <v>47</v>
+      </c>
+      <c r="E4" s="0">
+        <v>8</v>
+      </c>
+      <c r="F4" s="0">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>3561</v>
+      </c>
+      <c r="H4" s="0">
+        <v>352</v>
+      </c>
+      <c r="I4" s="0">
+        <v>43.3</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>3808</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>3809</v>
+      </c>
+      <c r="L4" s="0">
+        <v>87.8</v>
+      </c>
+      <c r="M4" s="0">
+        <v>3214</v>
+      </c>
+      <c r="N4" s="0">
+        <v>35</v>
+      </c>
+      <c r="O4" s="0">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="0">
+        <v>629</v>
+      </c>
+      <c r="C5" s="0">
+        <v>571</v>
+      </c>
+      <c r="D5" s="0">
+        <v>58</v>
+      </c>
+      <c r="E5" s="0">
+        <v>11</v>
+      </c>
+      <c r="F5" s="0">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>3568</v>
+      </c>
+      <c r="H5" s="0">
+        <v>241</v>
+      </c>
+      <c r="I5" s="0">
+        <v>38.4</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>3810</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>3811</v>
+      </c>
+      <c r="L5" s="0">
+        <v>82.6</v>
+      </c>
+      <c r="M5" s="0">
+        <v>2867</v>
+      </c>
+      <c r="N5" s="0">
+        <v>29</v>
+      </c>
+      <c r="O5" s="0">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="0">
+        <v>584</v>
+      </c>
+      <c r="C6" s="0">
+        <v>370</v>
+      </c>
+      <c r="D6" s="0">
+        <v>214</v>
+      </c>
+      <c r="E6" s="0">
+        <v>7</v>
+      </c>
+      <c r="F6" s="0">
+        <v>96</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>3568</v>
+      </c>
+      <c r="H6" s="0">
+        <v>175</v>
+      </c>
+      <c r="I6" s="0">
+        <v>35.9</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>3812</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>3813</v>
+      </c>
+      <c r="L6" s="0">
+        <v>94.7</v>
+      </c>
+      <c r="M6" s="0">
+        <v>3082</v>
+      </c>
+      <c r="N6" s="0">
+        <v>16</v>
+      </c>
+      <c r="O6" s="0">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="0">
+        <v>843</v>
+      </c>
+      <c r="C7" s="0">
+        <v>576</v>
+      </c>
+      <c r="D7" s="0">
+        <v>267</v>
+      </c>
+      <c r="E7" s="0">
+        <v>11</v>
+      </c>
+      <c r="F7" s="0">
+        <v>255</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>3574</v>
+      </c>
+      <c r="H7" s="0">
+        <v>188</v>
+      </c>
+      <c r="I7" s="0">
+        <v>32</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>3814</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>3815</v>
+      </c>
+      <c r="L7" s="0">
+        <v>76.5</v>
+      </c>
+      <c r="M7" s="0">
+        <v>2241</v>
+      </c>
+      <c r="N7" s="0">
+        <v>43</v>
+      </c>
+      <c r="O7" s="0">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="0">
+        <v>862</v>
+      </c>
+      <c r="C8" s="0">
+        <v>801</v>
+      </c>
+      <c r="D8" s="0">
+        <v>61</v>
+      </c>
+      <c r="E8" s="0">
+        <v>10</v>
+      </c>
+      <c r="F8" s="0">
+        <v>55</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>3574</v>
+      </c>
+      <c r="H8" s="0">
+        <v>369</v>
+      </c>
+      <c r="I8" s="0">
+        <v>45.7</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>3816</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>3817</v>
+      </c>
+      <c r="L8" s="0">
+        <v>71.6</v>
+      </c>
+      <c r="M8" s="0">
+        <v>2641</v>
+      </c>
+      <c r="N8" s="0">
+        <v>35</v>
+      </c>
+      <c r="O8" s="0">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="0">
+        <v>614</v>
+      </c>
+      <c r="C9" s="0">
+        <v>461</v>
+      </c>
+      <c r="D9" s="0">
+        <v>153</v>
+      </c>
+      <c r="E9" s="0">
+        <v>16</v>
+      </c>
+      <c r="F9" s="0">
+        <v>15</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>3574</v>
+      </c>
+      <c r="H9" s="0">
+        <v>225</v>
+      </c>
+      <c r="I9" s="0">
+        <v>37.6</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>3818</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>3819</v>
+      </c>
+      <c r="L9" s="0">
+        <v>64.1</v>
+      </c>
+      <c r="M9" s="0">
+        <v>1998</v>
+      </c>
+      <c r="N9" s="0">
+        <v>26</v>
+      </c>
+      <c r="O9" s="0">
+        <v>4.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O9"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:N81"/>
